--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3706000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4702000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3964000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3966000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4016000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5228000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4008000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3968000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3331000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5299000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3315000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2960000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3157000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4644000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2987000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2790000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2970000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3741000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2812000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2824000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3009000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4269000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2815000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2870000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2388000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2402000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2446000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3464000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2665000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2524000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1984000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3310000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2037000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1857000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1843000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3065000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1830000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1809000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1691000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2549000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1730000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1887000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1791000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2980000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1831000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1742000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1832000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1576000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1564000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1570000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1764000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1343000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1444000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1347000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1989000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1278000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1103000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1314000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1579000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1157000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>981000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1279000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1192000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1082000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>937000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1218000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1289000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>984000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>963000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E14" s="3">
         <v>536000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>53000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>148000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>45000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>942000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>118000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>478000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1405000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>43000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>53000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>39000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1354000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>65000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>84000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>425000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>170000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-4000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2687000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>66000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>716000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>16000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>664000</v>
+      </c>
+      <c r="E15" s="3">
         <v>665000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>650000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>656000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>639000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>738000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>601000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>583000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>561000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>599000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>533000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>525000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>504000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>490000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>489000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>484000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>470000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>459000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>321000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>480000</v>
       </c>
       <c r="W15" s="3">
         <v>480000</v>
       </c>
       <c r="X15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>466000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>463000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>462000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>506000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>524000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>512000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>499000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>503000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2915000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4210000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3240000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3346000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3252000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5272000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3504000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3709000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2710000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5427000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2730000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2561000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2363000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5023000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2487000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2488000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2683000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3105000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2312000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2472000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5050000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3530000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2395000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>791000</v>
+      </c>
+      <c r="E18" s="3">
         <v>492000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>724000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>620000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>764000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-44000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>504000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>259000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>621000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-128000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>585000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>399000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>794000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-379000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>302000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>287000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>636000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>500000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>352000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>739000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>420000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>330000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>553000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>470000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>471000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>567000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E20" s="3">
         <v>130000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>128000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>119000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>129000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>85000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>66000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>68000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>42000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>76000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>72000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>84000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>81000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>52000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>42000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>58000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>55000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>38000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>76000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>49000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>51000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>41000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>24000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>33000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1601000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1285000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1547000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1415000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1549000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>802000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1162000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>951000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1242000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>538000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1209000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1013000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1345000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>212000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1085000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>855000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>816000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1173000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>894000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>888000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1380000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1064000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>860000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>520000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E22" s="3">
         <v>433000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>392000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>361000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>350000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>302000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>271000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>246000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>231000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>245000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>232000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>217000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>226000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>222000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>229000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>225000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>222000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>214000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>211000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>194000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>196000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>188000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>180000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>170000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>166000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>162000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>159000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>152000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>150000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E23" s="3">
         <v>189000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>460000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>378000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>543000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-261000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>299000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>81000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>432000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-326000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>429000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>254000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>602000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-517000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>352000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>129000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>107000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>480000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>344000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>196000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>627000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>289000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>211000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>432000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>335000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>352000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>428000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-23000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>51000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>73000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-187000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-55000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-139000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>68000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-36000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>50000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-275000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-84000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-66000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-22000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-78000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-112000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-782000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>83000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>26000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>64000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E26" s="3">
         <v>212000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>409000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>365000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>470000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-74000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>292000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>136000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>571000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-297000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>361000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>290000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>552000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-242000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>348000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>213000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>173000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>502000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>422000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>308000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>544000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>298000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>242000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>501000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>309000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>392000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>364000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E27" s="3">
         <v>155000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>354000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>310000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>415000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-101000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>241000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>110000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>523000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-341000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>318000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>259000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>526000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>318000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>183000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>143000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>471000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>392000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>278000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>513000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>276000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>218000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>470000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>278000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>362000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>333000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,17 +2647,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2605,11 +2665,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>34000</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2617,12 +2677,12 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
@@ -2630,13 +2690,16 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>13000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-130000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-128000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-119000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-129000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-85000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-66000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-68000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-42000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-76000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-72000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-81000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-52000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-42000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-58000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-55000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-38000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-76000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E33" s="3">
         <v>155000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>354000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>310000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>415000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-101000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>241000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>110000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>523000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-341000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>318000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>259000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>526000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>318000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>183000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>143000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>471000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>392000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>278000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>513000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>276000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>218000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>470000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>278000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>362000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>346000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E35" s="3">
         <v>155000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>354000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>310000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>415000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-101000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>241000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>110000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>523000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-341000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>318000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>259000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>526000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>318000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>183000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>143000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>471000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>392000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>278000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>513000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>276000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>218000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>470000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>278000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>362000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>346000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E41" s="3">
         <v>446000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>836000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>914000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>232000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>122000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>231000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>390000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>524000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>84000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>389000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>87000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>92000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>524000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1337000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>68000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>547000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>257000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>328000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>144000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>71000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>99000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>105000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>117000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>98000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>150000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>96000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,560 +3625,581 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2016000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2363000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1717000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1451000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1695000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2259000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1547000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1312000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1398000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1612000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1314000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1696000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1906000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2314000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1044000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>926000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>906000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1226000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>922000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>908000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>921000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1211000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>954000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>760000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>941000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>833000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>688000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>714000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E44" s="3">
         <v>505000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>511000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>474000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>439000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>438000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>434000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>420000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>412000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>406000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>416000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>405000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>387000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>382000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>363000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>364000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>348000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>331000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>312000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>282000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>261000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>252000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>247000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>242000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>229000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>235000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>237000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>239000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3923000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3921000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4993000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4423000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3987000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3511000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3546000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3296000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3283000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3480000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3117000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2827000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2663000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3062000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2846000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2285000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2222000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2541000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2426000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2451000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2012000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1840000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1952000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>971000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6811000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7235000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7416000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7210000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7070000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6441000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5653000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5273000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5491000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6028000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4921000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5328000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5061000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5855000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4796000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4911000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3560000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4662000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3936000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3999000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3359000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3383000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3257000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4728000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4573000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4656000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4615000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4470000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4378000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4332000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4818000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5118000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4999000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5040000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4897000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4961000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4735000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4650000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4341000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4626000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4568000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4504000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4367000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4183000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4389000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4378000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57305000</v>
+      </c>
+      <c r="E48" s="3">
         <v>56346000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55557000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55516000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54928000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54129000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53446000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>52849000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>52632000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51286000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50036000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49355000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>48927000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>47582000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46225000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>45503000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>44978000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43940000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43156000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42697000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41348000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>40412000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>39831000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12914000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12010000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11922000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11513000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11573000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11761000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11614000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11780000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11504000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10710000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11165000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10925000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10423000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10384000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11380000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11271000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11218000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11042000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7925000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7730000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7825000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5379000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5354000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81758000</v>
+      </c>
+      <c r="E54" s="3">
         <v>80164000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>79551000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>78854000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78041000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76709000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75045000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74720000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74745000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>73023000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71162000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70505000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69372000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68556000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>67051000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>66026000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64382000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64212000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59521000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58793000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>56715000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>53563000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>52820000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1983000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2108000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1790000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1795000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2359000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2348000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2080000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1973000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2002000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2039000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1797000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1602000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1980000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1691000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1657000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1454000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1752000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1663000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1578000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1366000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1511000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1288000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1255000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>844000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3774000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3944000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4050000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3859000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4629000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5186000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4160000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3166000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3431000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3818000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3236000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3429000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3427000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2780000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1504000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2176000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1029000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1479000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1692000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1011000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>799000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>182000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>779000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>549000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2841000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2975000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2987000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2712000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3359000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3286000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3022000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3203000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3176000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3105000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2782000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4466000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4870000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4145000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2738000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2618000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2742000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2861000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2395000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2998000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3085000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3249000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2888000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8598000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9027000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8827000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8366000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10347000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10820000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9262000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8342000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8609000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8962000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7815000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9497000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10277000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8616000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5899000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6248000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5523000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6003000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5665000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5375000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5395000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4719000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4922000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30316000</v>
+      </c>
+      <c r="E61" s="3">
         <v>29532000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29430000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29442000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27025000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25145000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25143000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24967000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24170000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23342000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22891000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20165000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19632000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18958000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19238000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19125000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17864000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17066000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15883000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15683000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14632000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14629000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13845000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AD61" s="3">
         <v>11662000</v>
       </c>
       <c r="AE61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24900000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24034000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23600000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23497000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23147000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23451000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22965000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23779000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24177000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23977000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23143000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23620000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23514000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25333000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25468000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25109000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25499000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25790000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25060000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25016000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>24036000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>19926000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>20081000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66257000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64494000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63758000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63206000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62420000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61317000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59271000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>58989000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58857000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58182000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55750000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55183000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55324000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54808000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52798000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52675000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>48886000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48859000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46608000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46074000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>44063000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>39274000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38848000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,13 +6010,16 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1978000</v>
+        <v>1673000</v>
       </c>
       <c r="E70" s="3">
         <v>1978000</v>
@@ -5864,7 +6031,7 @@
         <v>1978000</v>
       </c>
       <c r="H70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="I70" s="3">
         <v>1977000</v>
@@ -5876,17 +6043,17 @@
         <v>1977000</v>
       </c>
       <c r="L70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="M70" s="3">
         <v>1235000</v>
       </c>
       <c r="N70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="O70" s="3">
         <v>1237000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -5897,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>2193000</v>
@@ -5924,13 +6091,13 @@
         <v>2193000</v>
       </c>
       <c r="AB70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AC70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AD70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AE70" s="3">
         <v>2191000</v>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>2191000</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>2191000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7499000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7399000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7553000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7456000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7454000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>7716000</v>
       </c>
       <c r="J72" s="3">
         <v>7716000</v>
       </c>
       <c r="K72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="L72" s="3">
         <v>7894000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7636000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8229000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8163000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8155000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7881000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8410000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8333000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8382000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8469000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8222000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8034000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7964000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>9597000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9286000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13828000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13692000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13815000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13670000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13643000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13415000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13797000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13754000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13911000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13606000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14177000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14085000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14048000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13748000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14253000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13351000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13303000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13160000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10720000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10526000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10459000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12096000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11779000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>378000</v>
+      </c>
+      <c r="E81" s="3">
         <v>155000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>354000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>310000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>415000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-101000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>241000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>110000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>523000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-341000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>318000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>259000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>526000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-288000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>318000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>183000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>143000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>471000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>392000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>278000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>513000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>276000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>218000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>470000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>278000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>362000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>346000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>687000</v>
+      </c>
+      <c r="E83" s="3">
         <v>663000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>695000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>676000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>656000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>761000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>592000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>624000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>579000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>619000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>548000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>542000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>517000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>507000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>504000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>501000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>487000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>479000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>339000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>498000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>301000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>565000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>595000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>479000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>524000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>543000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>528000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>520000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>523000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>855000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1834000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>802000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-90000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1104000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>874000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>446000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>792000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>427000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>958000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>72000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>192000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>446000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>310000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>315000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>510000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>388000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>210000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>906000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1054000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>401000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>816000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>899000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>554000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>884000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>754000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1457000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1339000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-986000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-891000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,34 +8117,35 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-278000</v>
+        <v>-279000</v>
       </c>
       <c r="E96" s="3">
         <v>-278000</v>
       </c>
       <c r="F96" s="3">
+        <v>-278000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-277000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-263000</v>
       </c>
       <c r="H96" s="3">
         <v>-263000</v>
       </c>
       <c r="I96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="J96" s="3">
         <v>-262000</v>
       </c>
       <c r="K96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="L96" s="3">
         <v>-247000</v>
@@ -7924,31 +8157,31 @@
         <v>-247000</v>
       </c>
       <c r="O96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="P96" s="3">
         <v>-237000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-228000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-226000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-216000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-195000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-199000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-197000</v>
       </c>
       <c r="X96" s="3">
         <v>-197000</v>
@@ -7960,25 +8193,28 @@
         <v>-197000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AD96" s="3">
         <v>-177000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-339000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1316000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1049000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>713000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>914000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>205000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>939000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>724000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2271000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1511000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1080000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>424000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-8000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2231000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>345000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2907000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>642000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1009000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>393000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-57000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>491000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>111000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>112000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>195000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E102" s="3">
         <v>251000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-640000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-79000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>684000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>110000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-111000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-160000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-131000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>440000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-305000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>301000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-432000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-812000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1268000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-478000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>283000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-120000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>233000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>73000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>997000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>19000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>55000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4078000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3706000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4702000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3964000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3966000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4016000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5228000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4008000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3968000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3331000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5299000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3315000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2960000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3157000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4644000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2987000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2790000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2970000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3741000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2812000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2824000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3009000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4269000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2325000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1964000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2870000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2388000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2402000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2446000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3464000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2665000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2524000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1984000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3310000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2037000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1857000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1843000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3065000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1830000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1809000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1691000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2549000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1730000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1887000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1791000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2980000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1753000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1742000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1832000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1576000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1564000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1570000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1764000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1343000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1444000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1347000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1989000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1278000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1103000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1314000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1579000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1157000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>981000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1279000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1192000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1082000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>937000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1218000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1289000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>984000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>963000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>651000</v>
+      </c>
+      <c r="E14" s="3">
         <v>144000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>536000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>53000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>148000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>45000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>942000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>118000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>478000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>58000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1405000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>43000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>53000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1354000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>65000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>84000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>425000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>170000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-4000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2687000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>66000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>716000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>16000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>702000</v>
+      </c>
+      <c r="E15" s="3">
         <v>664000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>665000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>650000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>656000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>639000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>738000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>601000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>583000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>561000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>599000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>533000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>525000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>504000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>490000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>489000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>484000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>470000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>459000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>321000</v>
-      </c>
-      <c r="W15" s="3">
-        <v>480000</v>
       </c>
       <c r="X15" s="3">
         <v>480000</v>
       </c>
       <c r="Y15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>466000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>463000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>462000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>506000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>524000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>512000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>499000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>503000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3833000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2915000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4210000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3240000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3346000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3252000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5272000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3504000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3709000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2710000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5427000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2730000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2561000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2363000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5023000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2487000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2488000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2683000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3105000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2312000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2472000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5050000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3530000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E18" s="3">
         <v>791000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>492000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>724000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>620000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>764000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>504000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>259000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>621000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-128000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>585000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>399000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>794000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-379000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>302000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>287000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>636000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>500000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>352000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>739000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>420000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>330000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>553000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>470000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>471000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>567000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E20" s="3">
         <v>123000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>130000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>128000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>119000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>129000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>85000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>66000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>68000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>42000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>47000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>76000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>72000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>34000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>84000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>81000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>52000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>42000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>58000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>55000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>38000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>76000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>49000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>51000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>34000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>41000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>24000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>33000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1090000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1601000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1285000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1547000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1415000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1549000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>802000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1162000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>951000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1242000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>538000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1209000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1013000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1345000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>212000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1085000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>855000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>816000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1173000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>894000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>888000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1380000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>860000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>520000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E22" s="3">
         <v>426000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>433000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>392000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>361000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>350000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>302000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>271000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>246000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>231000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>245000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>232000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>217000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>226000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>222000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>229000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>225000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>222000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>214000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>211000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>194000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>196000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>188000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>180000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>170000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>166000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>162000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>159000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>152000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>150000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E23" s="3">
         <v>488000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>189000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>460000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>378000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>543000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-261000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>299000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>81000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>432000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-326000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>429000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>254000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>602000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-517000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>352000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>129000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>107000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>480000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>344000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>196000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>627000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>289000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>211000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>432000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>335000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>352000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>428000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E24" s="3">
         <v>67000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-23000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>51000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>73000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-187000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-55000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-139000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-29000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>68000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-36000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-275000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-84000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-66000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-22000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-78000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-112000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-782000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>83000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>26000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>64000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E26" s="3">
         <v>421000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>212000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>409000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>365000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>470000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-74000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>292000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>136000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>571000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-297000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>361000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>290000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>552000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-242000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>348000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>213000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>173000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>502000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>422000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>308000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>544000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>298000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>242000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>501000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>309000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>392000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>364000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E27" s="3">
         <v>378000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>155000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>354000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>310000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>415000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-101000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>241000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>110000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>523000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-341000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>318000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>259000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>526000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-288000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>318000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>183000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>143000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>471000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>392000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>278000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>513000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>276000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>218000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>470000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>278000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>362000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>333000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,17 +2711,17 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2668,11 +2729,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>34000</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2680,12 +2741,12 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -2693,13 +2754,16 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>13000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-123000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-130000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-128000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-119000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-129000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-85000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-66000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-68000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-42000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-47000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-76000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-72000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-84000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-81000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-52000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-42000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-58000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-55000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-38000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-76000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E33" s="3">
         <v>378000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>155000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>354000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>310000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>415000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-101000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>241000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>110000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>523000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-341000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>318000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>259000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>526000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-288000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>318000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>183000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>143000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>471000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>392000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>278000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>513000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>276000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>218000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>470000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>278000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>362000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>346000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E35" s="3">
         <v>378000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>155000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>354000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>310000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>415000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-101000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>241000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>110000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>523000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-341000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>318000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>259000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>526000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-288000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>318000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>183000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>143000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>471000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>392000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>278000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>513000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>276000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>218000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>470000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>278000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>362000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>346000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>992000</v>
+      </c>
+      <c r="E41" s="3">
         <v>345000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>446000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>195000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>836000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>914000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>232000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>122000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>231000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>390000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>524000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>389000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>87000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>92000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>524000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1337000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>547000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>257000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>328000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>144000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>99000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>105000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>117000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>98000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>150000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>96000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,578 +3718,599 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1890000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2016000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2363000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1717000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1451000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1695000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2259000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1547000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1312000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1398000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1612000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1314000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1696000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1906000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2314000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1044000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>926000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>906000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1226000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>922000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>908000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>921000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1211000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>954000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>760000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>941000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>833000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>688000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>714000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E44" s="3">
         <v>527000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>505000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>511000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>500000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>474000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>439000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>438000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>434000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>420000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>412000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>406000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>416000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>405000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>387000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>382000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>363000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>364000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>348000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>331000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>312000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>282000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>261000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>252000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>247000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>242000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>229000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>235000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>237000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>239000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4477000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3923000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3921000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4993000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4423000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3987000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3511000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3546000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3296000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3283000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3480000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3117000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2827000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2663000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3062000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2846000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2285000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2222000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2541000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2426000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2451000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2012000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1840000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>971000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7878000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6811000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7235000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7416000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7210000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7070000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6441000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5653000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5273000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5491000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6028000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4921000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5328000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5061000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5855000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4796000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4911000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3560000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4662000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3936000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3999000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3359000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3383000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4849000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4728000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4573000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4656000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4615000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4470000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4378000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4332000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4818000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5118000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4999000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5040000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4897000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4961000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4735000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4650000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4341000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4626000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4568000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4504000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4367000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4183000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4389000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57894000</v>
+      </c>
+      <c r="E48" s="3">
         <v>57305000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56346000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55557000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55516000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54928000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54129000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>53446000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>52849000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>52632000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51286000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50036000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49355000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>48927000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>47582000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46225000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45503000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>44978000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43940000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43156000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42697000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41348000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40412000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12978000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12914000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12010000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11922000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11513000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11573000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11761000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11614000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11780000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11504000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10710000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11165000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10925000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10423000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10384000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11380000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11271000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11218000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11042000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7925000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7730000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7825000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5379000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83599000</v>
+      </c>
+      <c r="E54" s="3">
         <v>81758000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>80164000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79551000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78854000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78041000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76709000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75045000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74720000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74745000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73023000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>71162000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70505000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>69372000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68556000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>67051000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66026000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>64382000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64212000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59521000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58793000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>56715000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>53563000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1904000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1983000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2108000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1790000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1795000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2359000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2348000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2080000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1973000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2002000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2039000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1797000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1602000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1980000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1691000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1657000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1454000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1752000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1663000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1578000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1366000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1511000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1288000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>844000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2871000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3774000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3944000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4050000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3859000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4629000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5186000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4160000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3166000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3431000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3818000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3236000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3429000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3427000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2780000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1504000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2176000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1029000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1479000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1692000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1011000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>799000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>182000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>779000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>549000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3132000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2841000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2975000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2987000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2712000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3359000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3286000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3022000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3203000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3176000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3105000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2782000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4466000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4870000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4145000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2738000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2618000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2742000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2861000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2395000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2998000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3085000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3249000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7907000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8598000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9027000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8827000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8366000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10347000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10820000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9262000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8342000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8609000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8962000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7815000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9497000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10277000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8616000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5899000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6248000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5523000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6003000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5665000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5375000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5395000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4719000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>32576000</v>
+      </c>
+      <c r="E61" s="3">
         <v>30316000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29532000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29430000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29442000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27025000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25145000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25143000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24967000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24170000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23342000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22891000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20165000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19632000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18958000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19238000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19125000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17864000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17066000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15883000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15683000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14632000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14629000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AE61" s="3">
         <v>11662000</v>
       </c>
       <c r="AF61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25501000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24900000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24034000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23600000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23497000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23147000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23451000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22965000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23779000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24177000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23977000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23143000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23620000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23514000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25333000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25468000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25109000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25499000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25790000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25060000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25016000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>24036000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>19926000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68427000</v>
+      </c>
+      <c r="E66" s="3">
         <v>66257000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>64494000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>63758000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63206000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62420000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61317000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59271000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>58989000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58857000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58182000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55750000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55183000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55324000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54808000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52798000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52675000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>48886000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48859000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46608000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>46074000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>44063000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>39274000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,16 +6178,19 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="E70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>1978000</v>
       </c>
       <c r="F70" s="3">
         <v>1978000</v>
@@ -6034,7 +6202,7 @@
         <v>1978000</v>
       </c>
       <c r="I70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="J70" s="3">
         <v>1977000</v>
@@ -6046,17 +6214,17 @@
         <v>1977000</v>
       </c>
       <c r="M70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="N70" s="3">
         <v>1235000</v>
       </c>
       <c r="O70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="P70" s="3">
         <v>1237000</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -6067,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>2193000</v>
@@ -6094,13 +6262,13 @@
         <v>2193000</v>
       </c>
       <c r="AC70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AD70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AF70" s="3">
         <v>2191000</v>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>2191000</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>2191000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7166000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7499000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7399000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7553000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7456000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7454000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>7716000</v>
       </c>
       <c r="K72" s="3">
         <v>7716000</v>
       </c>
       <c r="L72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="M72" s="3">
         <v>7894000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7636000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8229000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8163000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8155000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7881000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8410000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8333000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8382000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8469000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8222000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8034000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7964000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9597000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13518000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13828000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13692000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13815000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13670000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13643000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13415000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13797000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13754000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13911000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13606000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14177000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14085000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14048000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13748000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14253000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13351000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13303000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13160000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10720000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10526000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10459000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12096000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E81" s="3">
         <v>378000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>155000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>354000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>310000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>415000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-101000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>241000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>110000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>523000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-341000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>318000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>259000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>526000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-288000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>318000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>183000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>143000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>471000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>392000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>278000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>513000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>276000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>218000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>470000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>278000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>362000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>346000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>707000</v>
+      </c>
+      <c r="E83" s="3">
         <v>687000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>663000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>695000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>676000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>656000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>761000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>592000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>624000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>579000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>619000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>548000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>542000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>517000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>507000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>504000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>501000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>487000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>479000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>339000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>498000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>301000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>565000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>595000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>479000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>524000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>543000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>528000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>520000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>523000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E89" s="3">
         <v>855000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1834000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>802000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-90000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1104000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>874000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>446000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>792000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>427000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>958000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>72000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>192000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>446000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>310000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>315000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>510000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>388000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>210000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>906000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1054000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>401000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>816000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>899000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>554000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>884000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>754000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1279000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1276000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-986000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,37 +8351,38 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-295000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-279000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-278000</v>
       </c>
       <c r="F96" s="3">
         <v>-278000</v>
       </c>
       <c r="G96" s="3">
+        <v>-278000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-277000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-263000</v>
       </c>
       <c r="I96" s="3">
         <v>-263000</v>
       </c>
       <c r="J96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="K96" s="3">
         <v>-262000</v>
       </c>
       <c r="L96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="M96" s="3">
         <v>-247000</v>
@@ -8160,31 +8394,31 @@
         <v>-247000</v>
       </c>
       <c r="P96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="Q96" s="3">
         <v>-237000</v>
       </c>
       <c r="R96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-228000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-226000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-216000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-195000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-199000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-197000</v>
       </c>
       <c r="Y96" s="3">
         <v>-197000</v>
@@ -8196,25 +8430,28 @@
         <v>-197000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AE96" s="3">
         <v>-177000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>988000</v>
+      </c>
+      <c r="E100" s="3">
         <v>567000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-339000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1316000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1049000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>713000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>914000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>205000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>939000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>724000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2271000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1511000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>424000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2231000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>345000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2907000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>642000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1009000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>393000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>491000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>111000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>112000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>195000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E102" s="3">
         <v>83000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>251000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-640000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-79000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>684000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>110000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-111000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-160000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-131000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>440000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-305000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>301000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-432000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-812000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1268000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-478000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>283000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-120000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>233000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>73000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>997000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>19000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>55000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4336000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4078000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3706000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4702000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3964000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3966000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4016000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5228000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4008000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3968000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3331000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5299000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3315000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2960000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3157000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4644000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2987000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2790000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2970000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3741000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2812000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2824000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3009000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2519000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2325000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1964000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2870000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2388000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2402000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2446000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3464000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2665000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2524000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1984000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3310000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2037000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1857000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1843000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3065000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1830000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1809000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1691000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2549000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1730000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1887000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1791000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1817000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1753000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1742000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1832000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1576000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1564000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1570000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1764000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1343000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1444000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1347000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1989000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1278000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1103000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1314000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1579000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1157000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>981000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1279000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1192000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1082000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>937000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1218000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>984000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>963000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E14" s="3">
         <v>651000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>144000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>536000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>53000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>148000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>45000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>942000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>118000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>478000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>58000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1405000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>43000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>53000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>39000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1354000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>65000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>84000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>425000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>170000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2687000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>66000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>716000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>16000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>726000</v>
+      </c>
+      <c r="E15" s="3">
         <v>702000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>664000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>665000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>650000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>656000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>639000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>738000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>601000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>583000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>561000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>599000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>533000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>525000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>504000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>490000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>489000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>484000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>470000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>459000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>321000</v>
-      </c>
-      <c r="X15" s="3">
-        <v>480000</v>
       </c>
       <c r="Y15" s="3">
         <v>480000</v>
       </c>
       <c r="Z15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>466000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>463000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>462000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>506000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>524000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>512000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>499000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>503000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3436000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3833000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2915000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4210000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3240000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3346000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3252000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5272000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3504000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3709000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2710000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5427000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2730000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2561000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2363000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5023000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2487000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2488000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2683000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3105000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2312000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2472000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5050000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>900000</v>
+      </c>
+      <c r="E18" s="3">
         <v>245000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>791000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>492000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>724000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>620000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>764000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-44000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>504000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>259000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>621000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-128000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>585000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>399000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>794000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-379000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>500000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>302000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>287000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>636000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>500000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>352000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>739000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>420000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>330000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>553000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>470000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>471000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>567000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E20" s="3">
         <v>138000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>123000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>130000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>128000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>119000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>129000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>85000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>66000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>68000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>42000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>47000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>76000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>72000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>34000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>84000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>81000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>52000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>42000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>58000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>55000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>38000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>76000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>49000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>51000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>34000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>41000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>24000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>33000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1795000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1090000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1601000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1285000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1547000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1415000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1549000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>802000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1162000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>951000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1242000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>538000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1209000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1013000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1345000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>212000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1085000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>855000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>816000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1173000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>894000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>888000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>860000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>520000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E22" s="3">
         <v>444000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>426000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>433000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>392000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>361000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>350000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>302000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>271000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>246000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>231000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>245000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>232000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>217000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>226000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>222000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>229000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>225000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>222000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>214000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>211000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>194000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>196000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>188000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>180000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>170000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>166000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>162000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>159000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>152000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>150000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-61000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>488000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>189000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>460000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>378000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>543000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-261000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>299000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>81000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>432000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-326000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>429000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>254000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>602000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-517000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>352000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>129000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>107000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>480000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>344000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>196000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>627000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>289000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>211000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>432000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>335000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>352000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>428000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-113000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>67000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-23000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>51000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>73000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-187000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-55000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-139000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-29000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>68000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-275000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-84000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-66000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-22000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-78000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-112000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-782000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>83000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>64000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E26" s="3">
         <v>52000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>421000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>212000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>409000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>365000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>470000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-74000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>292000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>136000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>571000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-297000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>361000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>290000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>552000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-242000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>348000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>213000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>173000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>502000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>422000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>308000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>544000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>298000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>242000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>501000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>309000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>392000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>364000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>378000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>155000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>354000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>310000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>415000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-101000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>241000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>110000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>523000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-341000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>318000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>259000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>526000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-288000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>318000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>183000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>143000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>471000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>392000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>278000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>513000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>276000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>218000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>470000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>278000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>362000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>333000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,17 +2775,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2732,11 +2793,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>34000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2744,12 +2805,12 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
@@ -2757,13 +2818,16 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>13000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-148000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-138000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-123000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-130000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-128000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-119000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-129000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-85000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-66000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-68000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-42000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-47000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-76000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-34000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-84000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-81000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-52000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-42000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-58000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-55000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>378000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>155000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>354000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>310000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>415000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-101000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>241000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>110000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>523000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-341000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>318000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>259000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>526000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-288000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>318000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>183000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>143000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>471000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>392000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>278000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>513000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>276000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>218000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>470000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>278000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>362000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>346000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>378000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>155000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>354000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>310000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>415000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-101000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>241000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>110000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>523000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-341000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>318000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>259000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>526000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-288000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>318000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>183000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>143000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>471000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>392000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>278000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>513000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>276000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>218000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>470000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>278000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>362000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>346000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E41" s="3">
         <v>992000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>345000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>446000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>195000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>836000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>914000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>232000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>122000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>231000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>390000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>524000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>389000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>87000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>524000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1337000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>68000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>547000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>257000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>328000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>144000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>71000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>99000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>105000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>117000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>98000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>150000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>96000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,596 +3811,617 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1890000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2016000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2363000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1717000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1451000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1695000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2259000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1547000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1312000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1398000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1612000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1314000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1696000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1906000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2314000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1044000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>926000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>906000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1226000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>922000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>908000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>921000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>954000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>760000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>941000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>833000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>688000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>714000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E44" s="3">
         <v>519000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>527000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>505000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>511000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>500000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>474000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>439000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>438000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>434000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>420000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>412000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>406000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>416000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>405000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>387000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>382000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>363000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>364000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>348000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>331000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>312000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>282000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>261000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>252000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>247000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>242000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>229000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>235000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>237000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>239000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5493000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4477000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3923000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3921000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4993000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4423000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3987000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3511000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3546000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3296000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3283000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3480000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3117000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2827000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2663000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3062000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2846000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2285000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2222000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2541000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2426000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2451000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2012000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>971000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8512000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7878000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6811000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7235000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7416000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7210000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7070000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6441000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5653000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5273000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5491000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6028000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4921000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5328000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5061000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5855000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4796000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4911000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3560000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4662000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3936000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3999000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3359000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4859000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4849000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4728000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4573000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4656000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4615000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4470000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4378000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4332000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4818000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5118000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4999000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5040000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4897000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4961000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4735000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4650000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4341000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4626000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4568000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4504000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4367000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4183000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>58550000</v>
+      </c>
+      <c r="E48" s="3">
         <v>57894000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57305000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56346000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55557000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55516000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54928000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54129000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>53446000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>52849000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52632000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51286000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50036000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49355000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>48927000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>47582000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46225000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45503000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>44978000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43940000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43156000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>42697000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41348000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12897000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12978000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12914000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12010000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11922000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11513000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11573000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11761000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11614000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11780000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11504000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10710000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11165000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10925000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10423000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10384000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11380000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11271000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11218000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11042000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7925000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7730000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7825000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84818000</v>
+      </c>
+      <c r="E54" s="3">
         <v>83599000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81758000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80164000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>79551000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78854000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78041000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76709000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>75045000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74720000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74745000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73023000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71162000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70505000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>69372000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68556000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>67051000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66026000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>64382000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64212000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59521000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58793000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>56715000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1892000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1904000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1983000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2108000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1790000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1795000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2359000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2348000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2080000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1973000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2002000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2039000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1797000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1602000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1980000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1691000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1657000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1454000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1752000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1663000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1578000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1366000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1511000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>844000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3203000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2871000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3774000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3944000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4050000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3859000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4629000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5186000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4160000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3166000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3431000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3818000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3236000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3429000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3427000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2780000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1504000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2176000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1029000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1479000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1692000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1011000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>799000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>182000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>779000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>549000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3179000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3132000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2841000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2975000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2987000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2712000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3359000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3286000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3022000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3203000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3176000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3105000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2782000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4466000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4870000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4145000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2738000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2618000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2742000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2861000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2395000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2998000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3085000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8274000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7907000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8598000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9027000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8827000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8366000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10347000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10820000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9262000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8342000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8609000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8962000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7815000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9497000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10277000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8616000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5899000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6248000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5523000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6003000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5665000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5375000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5395000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>33099000</v>
+      </c>
+      <c r="E61" s="3">
         <v>32576000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30316000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29532000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29430000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29442000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27025000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25145000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25143000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24967000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24170000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23342000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22891000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20165000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>19632000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>18958000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19238000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19125000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>17864000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17066000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15883000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15683000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14632000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AF61" s="3">
         <v>11662000</v>
       </c>
       <c r="AG61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25577000</v>
+      </c>
+      <c r="E62" s="3">
         <v>25501000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24900000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24034000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23600000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23497000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23147000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23451000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22965000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23779000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24177000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23977000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23143000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23620000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23514000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25333000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25468000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25109000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25499000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25790000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25060000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25016000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>24036000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69394000</v>
+      </c>
+      <c r="E66" s="3">
         <v>68427000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66257000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64494000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63758000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63206000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62420000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61317000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59271000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58989000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58857000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58182000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55750000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55183000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55324000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>54808000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52798000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>52675000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>48886000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48859000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>46608000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>46074000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>44063000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,19 +6346,22 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="E70" s="3">
         <v>1654000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1978000</v>
       </c>
       <c r="G70" s="3">
         <v>1978000</v>
@@ -6205,7 +6373,7 @@
         <v>1978000</v>
       </c>
       <c r="J70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="K70" s="3">
         <v>1977000</v>
@@ -6217,17 +6385,17 @@
         <v>1977000</v>
       </c>
       <c r="N70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="O70" s="3">
         <v>1235000</v>
       </c>
       <c r="P70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1237000</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -6238,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>2193000</v>
@@ -6265,13 +6433,13 @@
         <v>2193000</v>
       </c>
       <c r="AD70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AE70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AG70" s="3">
         <v>2191000</v>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>2191000</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>2191000</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7326000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7166000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7499000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7399000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7553000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7456000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7454000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>7716000</v>
       </c>
       <c r="L72" s="3">
         <v>7716000</v>
       </c>
       <c r="M72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="N72" s="3">
         <v>7894000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7636000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8229000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8163000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8155000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7881000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8410000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8333000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8382000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8469000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8222000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8034000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7964000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13779000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13518000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13828000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13692000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13815000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13670000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13643000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13415000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13797000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13754000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13911000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13606000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14177000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14085000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14048000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13748000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14253000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13351000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13303000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13160000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10720000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10526000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10459000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>378000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>155000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>354000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>310000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>415000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-101000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>241000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>110000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>523000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-341000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>318000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>259000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>526000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-288000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>318000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>183000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>143000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>471000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>392000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>278000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>513000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>276000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>218000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>470000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>278000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>362000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>346000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E83" s="3">
         <v>707000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>687000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>663000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>695000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>676000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>656000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>761000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>592000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>624000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>579000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>619000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>548000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>542000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>517000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>507000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>504000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>501000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>487000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>479000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>339000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>498000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>301000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>565000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>595000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>479000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>524000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>543000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>528000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>520000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>523000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1043000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>855000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1834000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>802000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-90000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1104000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>874000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>446000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>792000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>427000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>958000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>72000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>192000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>446000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>310000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>315000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>510000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>388000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>210000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>906000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>401000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>816000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>899000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>554000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>884000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>754000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1421000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1394000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-986000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,40 +8585,41 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-300000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-295000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-279000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-278000</v>
       </c>
       <c r="G96" s="3">
         <v>-278000</v>
       </c>
       <c r="H96" s="3">
+        <v>-278000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-277000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-263000</v>
       </c>
       <c r="J96" s="3">
         <v>-263000</v>
       </c>
       <c r="K96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="L96" s="3">
         <v>-262000</v>
       </c>
       <c r="M96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="N96" s="3">
         <v>-247000</v>
@@ -8397,31 +8631,31 @@
         <v>-247000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="R96" s="3">
         <v>-237000</v>
       </c>
       <c r="S96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-228000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-226000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-216000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-195000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-199000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-197000</v>
       </c>
       <c r="Z96" s="3">
         <v>-197000</v>
@@ -8433,25 +8667,28 @@
         <v>-197000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AF96" s="3">
         <v>-177000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E100" s="3">
         <v>988000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>567000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-339000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-97000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1316000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1049000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>713000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>914000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>205000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>939000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>724000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2271000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1511000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1080000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>424000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2231000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>345000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2907000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>642000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1009000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>393000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>491000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>111000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>112000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>195000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-488000</v>
+      </c>
+      <c r="E102" s="3">
         <v>755000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>83000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>251000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-640000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-79000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>684000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>110000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-111000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-160000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-131000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>440000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-305000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>301000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-432000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-812000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1268000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-478000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>283000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-120000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>233000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>73000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>997000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>19000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>55000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5201000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4336000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4078000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3706000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4702000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3964000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3966000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4016000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5228000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4008000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3968000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3331000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5299000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3315000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2960000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3157000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4644000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2987000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2790000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2970000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3741000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2812000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2824000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3244000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2519000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2325000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1964000</v>
-      </c>
       <c r="G9" s="3">
+        <v>-872000</v>
+      </c>
+      <c r="H9" s="3">
         <v>2870000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2388000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2402000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2446000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3464000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2665000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2524000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1984000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3310000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2037000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1857000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1843000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3065000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1830000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1809000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1691000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2549000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1730000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1887000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1957000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1817000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1753000</v>
       </c>
-      <c r="F10" s="3">
-        <v>1742000</v>
-      </c>
       <c r="G10" s="3">
+        <v>4578000</v>
+      </c>
+      <c r="H10" s="3">
         <v>1832000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1576000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1564000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1570000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1764000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1343000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1444000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1347000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1989000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1278000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1103000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1314000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1579000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1157000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>981000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1279000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1192000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1082000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>937000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>984000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>963000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1167,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>358000</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E14" s="3">
         <v>37000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>651000</v>
       </c>
-      <c r="F14" s="3">
-        <v>144000</v>
-      </c>
       <c r="G14" s="3">
+        <v>140000</v>
+      </c>
+      <c r="H14" s="3">
         <v>536000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>53000</v>
       </c>
-      <c r="I14" s="3">
-        <v>148000</v>
-      </c>
       <c r="J14" s="3">
+        <v>151000</v>
+      </c>
+      <c r="K14" s="3">
         <v>45000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>942000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>118000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>478000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>58000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1405000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>43000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>53000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1354000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>65000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>84000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>425000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>170000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>66000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>716000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>16000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E15" s="3">
         <v>726000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>702000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>664000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>665000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>650000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>656000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>639000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>738000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>601000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>583000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>561000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>599000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>533000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>525000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>504000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>490000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>489000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>484000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>470000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>459000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>321000</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>480000</v>
       </c>
       <c r="Z15" s="3">
         <v>480000</v>
       </c>
       <c r="AA15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AB15" s="3">
         <v>466000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>463000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>462000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>506000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>524000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>512000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>499000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>503000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3436000</v>
+        <v>4100000</v>
       </c>
       <c r="E17" s="3">
-        <v>3833000</v>
+        <v>3377000</v>
       </c>
       <c r="F17" s="3">
-        <v>2915000</v>
+        <v>3160000</v>
       </c>
       <c r="G17" s="3">
-        <v>4210000</v>
+        <v>2752000</v>
       </c>
       <c r="H17" s="3">
-        <v>3240000</v>
+        <v>3648000</v>
       </c>
       <c r="I17" s="3">
-        <v>3346000</v>
+        <v>3161000</v>
       </c>
       <c r="J17" s="3">
+        <v>3172000</v>
+      </c>
+      <c r="K17" s="3">
         <v>3252000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5272000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3504000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3709000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2710000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5427000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2730000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2561000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2363000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5023000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2487000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2488000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2683000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3105000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2312000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2472000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>900000</v>
+        <v>1101000</v>
       </c>
       <c r="E18" s="3">
-        <v>245000</v>
+        <v>959000</v>
       </c>
       <c r="F18" s="3">
-        <v>791000</v>
+        <v>918000</v>
       </c>
       <c r="G18" s="3">
-        <v>492000</v>
+        <v>954000</v>
       </c>
       <c r="H18" s="3">
-        <v>724000</v>
+        <v>1054000</v>
       </c>
       <c r="I18" s="3">
-        <v>620000</v>
+        <v>803000</v>
       </c>
       <c r="J18" s="3">
+        <v>794000</v>
+      </c>
+      <c r="K18" s="3">
         <v>764000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-44000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>504000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>259000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>621000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-128000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>585000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>399000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>794000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-379000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>302000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>287000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>636000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>500000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>352000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>739000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>420000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>330000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>553000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>470000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>471000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>567000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>148000</v>
+        <v>-40000</v>
       </c>
       <c r="E20" s="3">
-        <v>138000</v>
+        <v>-53000</v>
       </c>
       <c r="F20" s="3">
-        <v>123000</v>
+        <v>-49000</v>
       </c>
       <c r="G20" s="3">
-        <v>130000</v>
+        <v>-294000</v>
       </c>
       <c r="H20" s="3">
-        <v>128000</v>
+        <v>-34000</v>
       </c>
       <c r="I20" s="3">
-        <v>119000</v>
+        <v>-35000</v>
       </c>
       <c r="J20" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="K20" s="3">
         <v>129000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>85000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>66000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>68000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>42000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>47000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>76000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>72000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>34000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>81000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>52000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>42000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>58000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>55000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>38000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>76000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>49000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>51000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>41000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>24000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>33000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1795000</v>
+        <v>1851000</v>
       </c>
       <c r="E21" s="3">
-        <v>1090000</v>
+        <v>1738000</v>
       </c>
       <c r="F21" s="3">
-        <v>1601000</v>
+        <v>1669000</v>
       </c>
       <c r="G21" s="3">
-        <v>1285000</v>
+        <v>1912000</v>
       </c>
       <c r="H21" s="3">
-        <v>1547000</v>
+        <v>1753000</v>
       </c>
       <c r="I21" s="3">
-        <v>1415000</v>
+        <v>1488000</v>
       </c>
       <c r="J21" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1549000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>802000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1162000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>951000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1242000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>538000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1013000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1345000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>212000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1085000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>855000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>816000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1173000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>894000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>888000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>860000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>520000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E22" s="3">
         <v>480000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>444000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>426000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>433000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>392000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>361000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>350000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>302000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>271000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>246000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>231000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>245000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>232000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>217000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>226000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>222000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>229000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>225000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>222000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>214000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>211000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>194000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>196000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>188000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>180000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>170000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>166000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>162000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>159000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>152000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>150000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>568000</v>
+        <v>584000</v>
       </c>
       <c r="E23" s="3">
-        <v>-61000</v>
+        <v>498000</v>
       </c>
       <c r="F23" s="3">
-        <v>488000</v>
+        <v>-124000</v>
       </c>
       <c r="G23" s="3">
-        <v>189000</v>
+        <v>445000</v>
       </c>
       <c r="H23" s="3">
-        <v>460000</v>
+        <v>132000</v>
       </c>
       <c r="I23" s="3">
-        <v>378000</v>
+        <v>405000</v>
       </c>
       <c r="J23" s="3">
+        <v>323000</v>
+      </c>
+      <c r="K23" s="3">
         <v>543000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-261000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>299000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>81000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>432000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-326000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>429000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>254000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>602000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-517000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>352000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>129000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>107000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>480000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>344000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>196000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>627000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>289000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>211000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>432000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>335000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>352000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>428000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E24" s="3">
         <v>59000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-113000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>67000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-23000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>51000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>73000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-187000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-55000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-139000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-29000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>68000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-36000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-275000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-84000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-66000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-22000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-78000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-112000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>83000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>26000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>64000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>509000</v>
+        <v>516000</v>
       </c>
       <c r="E26" s="3">
-        <v>52000</v>
+        <v>439000</v>
       </c>
       <c r="F26" s="3">
-        <v>421000</v>
+        <v>-11000</v>
       </c>
       <c r="G26" s="3">
-        <v>212000</v>
+        <v>378000</v>
       </c>
       <c r="H26" s="3">
-        <v>409000</v>
+        <v>155000</v>
       </c>
       <c r="I26" s="3">
-        <v>365000</v>
+        <v>354000</v>
       </c>
       <c r="J26" s="3">
+        <v>310000</v>
+      </c>
+      <c r="K26" s="3">
         <v>470000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-74000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>292000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>136000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>571000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-297000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>361000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>290000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>552000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-242000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>348000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>213000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>173000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>502000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>422000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>308000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>544000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>298000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>242000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>501000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>309000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>392000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>364000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E27" s="3">
         <v>439000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>378000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>155000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>354000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>310000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>415000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-101000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>241000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>110000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>523000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-341000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>318000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>259000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>526000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-288000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>318000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>183000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>143000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>471000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>392000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>278000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>513000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>276000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>218000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>470000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>278000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>362000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>333000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,17 +2839,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2796,11 +2857,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2808,12 +2869,12 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
@@ -2821,13 +2882,16 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>13000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-148000</v>
+        <v>40000</v>
       </c>
       <c r="E32" s="3">
-        <v>-138000</v>
+        <v>53000</v>
       </c>
       <c r="F32" s="3">
-        <v>-123000</v>
+        <v>49000</v>
       </c>
       <c r="G32" s="3">
-        <v>-130000</v>
+        <v>294000</v>
       </c>
       <c r="H32" s="3">
-        <v>-128000</v>
+        <v>34000</v>
       </c>
       <c r="I32" s="3">
-        <v>-119000</v>
+        <v>35000</v>
       </c>
       <c r="J32" s="3">
+        <v>34000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-129000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-85000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-66000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-68000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-42000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-47000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-72000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-34000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-81000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-52000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-42000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-58000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E33" s="3">
         <v>439000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>378000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>155000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>354000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>310000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>415000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-101000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>241000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>110000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>523000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-341000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>318000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>259000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>526000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-288000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>318000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>183000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>143000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>471000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>392000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>278000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>513000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>276000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>218000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>470000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>278000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>362000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>346000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E35" s="3">
         <v>439000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>378000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>155000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>354000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>310000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>415000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-101000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>241000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>110000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>523000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-341000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>318000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>259000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>526000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-288000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>318000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>183000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>143000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>471000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>392000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>278000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>513000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>276000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>218000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>470000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>278000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>362000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>346000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E41" s="3">
         <v>465000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>992000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>345000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>446000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>195000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>836000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>914000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>232000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>231000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>390000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>524000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>389000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>87000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>524000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1337000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>547000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>257000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>328000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>144000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>71000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>99000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>105000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>117000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>98000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>150000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>96000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,614 +3904,635 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2020000</v>
+        <v>3982000</v>
       </c>
       <c r="E43" s="3">
-        <v>1890000</v>
+        <v>3027000</v>
       </c>
       <c r="F43" s="3">
-        <v>2016000</v>
+        <v>2667000</v>
       </c>
       <c r="G43" s="3">
-        <v>2363000</v>
+        <v>2758000</v>
       </c>
       <c r="H43" s="3">
-        <v>1717000</v>
+        <v>3292000</v>
       </c>
       <c r="I43" s="3">
-        <v>1451000</v>
+        <v>2473000</v>
       </c>
       <c r="J43" s="3">
+        <v>2217000</v>
+      </c>
+      <c r="K43" s="3">
         <v>1695000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2259000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1547000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1312000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1398000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1612000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1314000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1696000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1906000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2314000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1044000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>926000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>906000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1226000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>922000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>908000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>921000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>954000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>760000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>941000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>833000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>688000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>714000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E44" s="3">
         <v>534000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>519000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>527000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>505000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>511000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>500000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>474000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>439000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>438000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>434000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>420000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>412000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>406000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>416000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>405000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>387000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>382000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>363000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>364000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>348000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>331000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>312000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>282000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>261000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>252000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>247000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>242000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>229000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>235000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>237000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>239000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5493000</v>
+        <v>2558000</v>
       </c>
       <c r="E45" s="3">
-        <v>4477000</v>
+        <v>4344000</v>
       </c>
       <c r="F45" s="3">
-        <v>3923000</v>
+        <v>3389000</v>
       </c>
       <c r="G45" s="3">
-        <v>3921000</v>
+        <v>3034000</v>
       </c>
       <c r="H45" s="3">
-        <v>4993000</v>
+        <v>2887000</v>
       </c>
       <c r="I45" s="3">
-        <v>4423000</v>
+        <v>4146000</v>
       </c>
       <c r="J45" s="3">
+        <v>3344000</v>
+      </c>
+      <c r="K45" s="3">
         <v>3987000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3511000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3546000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3296000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3283000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3480000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3117000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2827000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2663000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3062000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2846000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2285000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2222000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2541000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2426000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2451000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>971000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7444000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8512000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7878000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6811000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7235000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7416000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7210000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7070000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6441000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5653000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5273000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5491000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6028000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4921000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5328000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5061000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5855000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4796000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4911000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3560000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4662000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3936000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3999000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4859000</v>
+        <v>50000</v>
       </c>
       <c r="E47" s="3">
-        <v>4849000</v>
+        <v>71000</v>
       </c>
       <c r="F47" s="3">
-        <v>4728000</v>
+        <v>62000</v>
       </c>
       <c r="G47" s="3">
-        <v>4573000</v>
+        <v>54000</v>
       </c>
       <c r="H47" s="3">
-        <v>4656000</v>
+        <v>81000</v>
       </c>
       <c r="I47" s="3">
-        <v>4615000</v>
+        <v>72000</v>
       </c>
       <c r="J47" s="3">
+        <v>64000</v>
+      </c>
+      <c r="K47" s="3">
         <v>4470000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4378000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4332000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4818000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5118000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4999000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5040000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4897000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4961000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4735000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4650000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4341000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4626000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4568000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4504000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4367000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>59478000</v>
+      </c>
+      <c r="E48" s="3">
         <v>58550000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57894000</v>
       </c>
-      <c r="F48" s="3">
-        <v>57305000</v>
-      </c>
       <c r="G48" s="3">
+        <v>57183000</v>
+      </c>
+      <c r="H48" s="3">
         <v>56346000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55557000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55516000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54928000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54129000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>53446000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52849000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52632000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51286000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50036000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49355000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>48927000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>47582000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>46225000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45503000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>44978000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43940000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43156000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>42697000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12897000</v>
+        <v>9117000</v>
       </c>
       <c r="E52" s="3">
-        <v>12978000</v>
+        <v>9027000</v>
       </c>
       <c r="F52" s="3">
-        <v>12914000</v>
+        <v>8959000</v>
       </c>
       <c r="G52" s="3">
-        <v>12010000</v>
+        <v>8813000</v>
       </c>
       <c r="H52" s="3">
-        <v>11922000</v>
+        <v>7728000</v>
       </c>
       <c r="I52" s="3">
-        <v>11513000</v>
+        <v>7885000</v>
       </c>
       <c r="J52" s="3">
+        <v>7913000</v>
+      </c>
+      <c r="K52" s="3">
         <v>11573000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11761000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11614000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11780000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11504000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10710000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11165000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10925000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10423000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10384000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11380000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11271000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11218000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11042000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7925000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7730000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>84749000</v>
+      </c>
+      <c r="E54" s="3">
         <v>84818000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>83599000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81758000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80164000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>79551000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>78854000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78041000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76709000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75045000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74720000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74745000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73023000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>71162000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70505000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>69372000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>68556000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>67051000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66026000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64382000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64212000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59521000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>58793000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1892000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1904000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1983000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2108000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1790000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1795000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2359000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2348000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2080000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1973000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2002000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2039000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1797000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1602000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1980000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1691000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1657000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1454000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1752000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1663000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1578000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1366000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>844000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3203000</v>
+        <v>3240000</v>
       </c>
       <c r="E58" s="3">
-        <v>2871000</v>
+        <v>3328000</v>
       </c>
       <c r="F58" s="3">
-        <v>3774000</v>
+        <v>2990000</v>
       </c>
       <c r="G58" s="3">
-        <v>3944000</v>
+        <v>3894000</v>
       </c>
       <c r="H58" s="3">
-        <v>4050000</v>
+        <v>4123000</v>
       </c>
       <c r="I58" s="3">
-        <v>3859000</v>
+        <v>4365000</v>
       </c>
       <c r="J58" s="3">
+        <v>4279000</v>
+      </c>
+      <c r="K58" s="3">
         <v>4629000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5186000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4160000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3166000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3431000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3818000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3236000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3429000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3427000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2780000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1504000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2176000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1029000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1479000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1692000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1011000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>799000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>182000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>779000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>549000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3179000</v>
+        <v>2630000</v>
       </c>
       <c r="E59" s="3">
-        <v>3132000</v>
+        <v>2611000</v>
       </c>
       <c r="F59" s="3">
-        <v>2841000</v>
+        <v>2573000</v>
       </c>
       <c r="G59" s="3">
-        <v>2975000</v>
+        <v>2721000</v>
       </c>
       <c r="H59" s="3">
-        <v>2987000</v>
+        <v>2796000</v>
       </c>
       <c r="I59" s="3">
-        <v>2712000</v>
+        <v>2672000</v>
       </c>
       <c r="J59" s="3">
+        <v>2292000</v>
+      </c>
+      <c r="K59" s="3">
         <v>3359000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3286000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3022000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3203000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3176000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3105000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2782000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4466000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4870000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4145000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2738000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2618000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2742000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2861000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2395000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2998000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8507000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8274000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7907000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8598000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9027000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8827000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8366000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10347000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10820000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9262000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8342000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8609000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8962000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7815000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9497000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10277000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8616000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5899000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6248000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5523000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6003000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5665000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5375000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>33099000</v>
+        <v>33359000</v>
       </c>
       <c r="E61" s="3">
-        <v>32576000</v>
+        <v>34175000</v>
       </c>
       <c r="F61" s="3">
-        <v>30316000</v>
+        <v>33663000</v>
       </c>
       <c r="G61" s="3">
-        <v>29532000</v>
+        <v>31417000</v>
       </c>
       <c r="H61" s="3">
-        <v>29430000</v>
+        <v>30645000</v>
       </c>
       <c r="I61" s="3">
-        <v>29442000</v>
+        <v>30346000</v>
       </c>
       <c r="J61" s="3">
+        <v>30368000</v>
+      </c>
+      <c r="K61" s="3">
         <v>27025000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25145000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25143000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24967000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24170000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23342000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22891000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20165000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19632000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18958000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19238000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19125000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17864000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17066000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15883000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15683000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AG61" s="3">
         <v>11662000</v>
       </c>
       <c r="AH61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>25577000</v>
+        <v>13540000</v>
       </c>
       <c r="E62" s="3">
-        <v>25501000</v>
+        <v>13361000</v>
       </c>
       <c r="F62" s="3">
-        <v>24900000</v>
+        <v>13460000</v>
       </c>
       <c r="G62" s="3">
-        <v>24034000</v>
+        <v>12482000</v>
       </c>
       <c r="H62" s="3">
-        <v>23600000</v>
+        <v>12443000</v>
       </c>
       <c r="I62" s="3">
-        <v>23497000</v>
+        <v>12269000</v>
       </c>
       <c r="J62" s="3">
+        <v>12642000</v>
+      </c>
+      <c r="K62" s="3">
         <v>23147000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23451000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22965000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23779000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24177000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23977000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23143000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23620000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23514000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25333000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25468000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25109000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25499000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25790000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25060000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25016000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>69394000</v>
+        <v>66642000</v>
       </c>
       <c r="E66" s="3">
-        <v>68427000</v>
+        <v>66950000</v>
       </c>
       <c r="F66" s="3">
-        <v>66257000</v>
+        <v>65984000</v>
       </c>
       <c r="G66" s="3">
-        <v>64494000</v>
+        <v>63814000</v>
       </c>
       <c r="H66" s="3">
-        <v>63758000</v>
+        <v>62593000</v>
       </c>
       <c r="I66" s="3">
-        <v>63206000</v>
+        <v>61857000</v>
       </c>
       <c r="J66" s="3">
+        <v>61305000</v>
+      </c>
+      <c r="K66" s="3">
         <v>62420000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61317000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59271000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58989000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58857000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58182000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55750000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55183000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55324000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>54808000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>52798000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>52675000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>48886000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48859000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>46608000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>46074000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6358,13 +6526,13 @@
         <v>1645000</v>
       </c>
       <c r="E70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="F70" s="3">
         <v>1654000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1978000</v>
       </c>
       <c r="H70" s="3">
         <v>1978000</v>
@@ -6376,7 +6544,7 @@
         <v>1978000</v>
       </c>
       <c r="K70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="L70" s="3">
         <v>1977000</v>
@@ -6388,17 +6556,17 @@
         <v>1977000</v>
       </c>
       <c r="O70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="P70" s="3">
         <v>1235000</v>
       </c>
       <c r="Q70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="R70" s="3">
         <v>1237000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -6409,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3">
         <v>2193000</v>
@@ -6436,13 +6604,13 @@
         <v>2193000</v>
       </c>
       <c r="AE70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AF70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AG70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AH70" s="3">
         <v>2191000</v>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7486000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7326000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7166000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7499000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7399000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7553000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7456000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7454000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>7716000</v>
       </c>
       <c r="M72" s="3">
         <v>7716000</v>
       </c>
       <c r="N72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="O72" s="3">
         <v>7894000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7636000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8229000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8163000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8155000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7881000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8410000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8333000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8382000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8469000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8222000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8034000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14018000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13779000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13518000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13828000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13692000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13815000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13670000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13643000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13415000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13797000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13754000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13911000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13606000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14177000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14085000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14048000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13748000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14253000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13351000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13303000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13160000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10720000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10526000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>516000</v>
+      </c>
+      <c r="E81" s="3">
         <v>439000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>378000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>155000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>354000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>310000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>415000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-101000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>241000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>110000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>523000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-341000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>318000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>259000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>526000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-288000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>318000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>183000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>143000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>471000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>392000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>278000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>513000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>276000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>218000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>470000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>278000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>362000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>346000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>747000</v>
+        <v>663000</v>
       </c>
       <c r="E83" s="3">
-        <v>707000</v>
+        <v>695000</v>
       </c>
       <c r="F83" s="3">
-        <v>687000</v>
+        <v>676000</v>
       </c>
       <c r="G83" s="3">
-        <v>663000</v>
+        <v>312000</v>
       </c>
       <c r="H83" s="3">
-        <v>695000</v>
+        <v>761000</v>
       </c>
       <c r="I83" s="3">
-        <v>676000</v>
+        <v>592000</v>
       </c>
       <c r="J83" s="3">
+        <v>624000</v>
+      </c>
+      <c r="K83" s="3">
         <v>656000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>761000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>592000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>624000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>579000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>619000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>548000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>542000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>517000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>507000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>504000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>501000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>487000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>479000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>339000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>498000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>301000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>565000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>595000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>479000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>524000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>543000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>528000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>520000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>523000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2472000</v>
+      </c>
+      <c r="E89" s="3">
         <v>329000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1043000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>855000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1834000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>802000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-90000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1104000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>874000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>446000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>792000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>427000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>958000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>72000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>192000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>446000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>310000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>315000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>510000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>388000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>210000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>906000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>401000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>816000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>899000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>554000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>884000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>754000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1511000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1427000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-986000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,43 +8819,44 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-300000</v>
+        <v>301000</v>
       </c>
       <c r="E96" s="3">
-        <v>-295000</v>
+        <v>300000</v>
       </c>
       <c r="F96" s="3">
-        <v>-279000</v>
+        <v>295000</v>
       </c>
       <c r="G96" s="3">
-        <v>-278000</v>
+        <v>279000</v>
       </c>
       <c r="H96" s="3">
-        <v>-278000</v>
+        <v>278000</v>
       </c>
       <c r="I96" s="3">
-        <v>-277000</v>
+        <v>278000</v>
       </c>
       <c r="J96" s="3">
-        <v>-263000</v>
+        <v>277000</v>
       </c>
       <c r="K96" s="3">
         <v>-263000</v>
       </c>
       <c r="L96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="M96" s="3">
         <v>-262000</v>
       </c>
       <c r="N96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="O96" s="3">
         <v>-247000</v>
@@ -8634,31 +8868,31 @@
         <v>-247000</v>
       </c>
       <c r="R96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="S96" s="3">
         <v>-237000</v>
       </c>
       <c r="T96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-228000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-226000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-216000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-195000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-199000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AA96" s="3">
         <v>-197000</v>
@@ -8670,25 +8904,28 @@
         <v>-197000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AG96" s="3">
         <v>-177000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1201000</v>
+      </c>
+      <c r="E100" s="3">
         <v>577000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>988000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>567000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-339000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-97000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1316000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1049000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>713000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>914000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>205000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>939000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>724000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2271000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1511000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1080000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>424000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2231000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>345000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2907000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>642000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1009000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>393000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>491000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>111000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>112000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>195000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-156000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-488000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>755000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>251000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-640000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-79000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>684000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>110000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-111000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-160000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-131000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>440000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-305000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>301000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-432000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-812000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1268000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-478000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>283000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>233000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>73000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>997000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>19000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>55000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3984000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5201000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4336000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4078000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3706000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4702000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3964000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3966000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4016000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5228000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4008000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3968000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3331000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5299000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3315000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2960000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3157000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4644000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2987000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2790000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2970000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3741000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2812000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2824000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3244000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2519000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2325000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>-872000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2870000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2388000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2402000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2446000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3464000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2665000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2524000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1984000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3310000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2037000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1857000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1843000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3065000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1830000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1809000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1691000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2549000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1730000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1887000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3623000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1957000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1817000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1753000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4578000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1832000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1576000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1564000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1570000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1764000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1343000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1444000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1347000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1989000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1278000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1103000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1314000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1579000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1157000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>981000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1279000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1192000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1082000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>937000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>984000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>963000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,13 +1165,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>416000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1167,11 +1180,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>358000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,216 +1377,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E14" s="3">
         <v>84000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>37000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>651000</v>
       </c>
-      <c r="G14" s="3">
-        <v>140000</v>
-      </c>
       <c r="H14" s="3">
+        <v>144000</v>
+      </c>
+      <c r="I14" s="3">
         <v>536000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>53000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>151000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>45000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>942000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>118000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>478000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>58000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1405000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>53000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1354000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>65000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>84000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>425000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>170000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>66000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>716000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>16000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E15" s="3">
         <v>710000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>726000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>702000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>664000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>665000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>650000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>656000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>639000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>738000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>601000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>583000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>561000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>599000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>533000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>525000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>504000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>490000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>489000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>484000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>470000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>459000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>321000</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>480000</v>
       </c>
       <c r="AA15" s="3">
         <v>480000</v>
       </c>
       <c r="AB15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>466000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>463000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>462000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>506000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>524000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>512000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>499000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>503000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3090000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4100000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3377000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3160000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2752000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2749000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3648000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3161000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3172000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3252000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5272000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3504000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3709000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2710000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5427000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2730000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2561000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2363000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5023000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2487000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2488000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2683000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3105000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2312000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2472000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1101000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>959000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>918000</v>
       </c>
-      <c r="G18" s="3">
-        <v>954000</v>
-      </c>
       <c r="H18" s="3">
+        <v>957000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1054000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>803000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>794000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>764000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-44000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>504000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>259000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>621000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-128000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>585000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>399000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>794000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-379000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>500000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>302000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>287000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>636000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>500000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>352000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>739000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>420000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>330000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>553000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>470000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>471000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>567000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-40000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-53000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-49000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-294000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-34000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-35000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>129000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>85000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>66000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>68000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>42000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>47000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>76000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>72000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>34000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>84000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>81000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>52000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>42000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>58000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>55000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>38000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>76000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>49000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>51000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>41000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>24000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>33000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1632000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1851000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1738000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1669000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1912000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1753000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1488000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1484000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1549000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>802000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1162000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>951000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1242000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>538000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1209000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1013000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1345000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>212000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1085000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>855000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>816000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1173000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>894000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>888000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>860000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>520000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E22" s="3">
         <v>477000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>480000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>444000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>426000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>433000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>392000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>361000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>350000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>302000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>271000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>246000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>231000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>245000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>232000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>217000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>226000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>222000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>229000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>225000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>222000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>214000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>211000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>194000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>196000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>188000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>180000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>170000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>166000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>162000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>159000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>152000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>150000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E23" s="3">
         <v>584000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>498000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-124000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>445000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>132000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>405000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>323000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>543000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-261000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>299000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>81000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>432000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-326000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>429000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>254000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>602000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-517000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>352000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>129000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>107000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>480000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>344000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>196000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>627000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>289000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>211000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>432000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>335000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>352000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>428000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>68000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>59000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-113000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>67000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-23000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>51000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>73000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-187000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-55000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-139000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>68000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-36000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-275000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-84000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-66000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-78000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>83000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E26" s="3">
         <v>516000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>439000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>378000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>155000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>354000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>310000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>470000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-74000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>292000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>136000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>571000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-297000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>361000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>290000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>552000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-242000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>348000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>213000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>173000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>502000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>422000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>308000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>544000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>298000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>242000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>501000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>309000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>392000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>364000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E27" s="3">
         <v>516000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>439000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>378000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>155000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>354000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>310000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>415000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-101000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>241000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>523000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-341000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>318000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>259000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>526000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-288000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>318000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>183000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>143000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>471000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>392000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>278000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>513000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>276000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>218000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>470000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>278000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>362000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>333000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2842,17 +2902,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2860,11 +2920,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2872,12 +2932,12 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
@@ -2885,13 +2945,16 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>13000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>40000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>53000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>49000</v>
       </c>
-      <c r="G32" s="3">
-        <v>294000</v>
-      </c>
       <c r="H32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="I32" s="3">
         <v>34000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>35000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-129000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-85000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-66000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-68000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-42000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-76000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-72000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-34000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-84000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-81000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-52000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-42000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E33" s="3">
         <v>516000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>439000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>378000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>155000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>354000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>310000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>415000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-101000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>241000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>110000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>523000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-341000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>318000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>259000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>526000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-288000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>318000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>183000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>143000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>471000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>392000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>278000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>513000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>276000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>218000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>470000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>278000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>362000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E35" s="3">
         <v>516000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>439000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>378000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>155000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>354000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>310000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>415000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-101000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>241000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>110000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>523000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-341000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>318000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>259000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>526000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-288000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>318000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>183000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>143000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>471000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>392000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>278000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>513000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>276000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>218000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>470000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>278000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>362000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E41" s="3">
         <v>200000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>465000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>992000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>345000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>446000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>195000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>836000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>914000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>232000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>122000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>231000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>390000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>524000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>389000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>87000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>92000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>524000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1337000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>68000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>547000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>257000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>328000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>144000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>71000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>99000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>105000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>117000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>98000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>150000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,632 +3996,653 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3017000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3982000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3027000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2667000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2758000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3292000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2473000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2217000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1695000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2259000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1547000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1312000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1398000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1612000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1314000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1696000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1906000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2314000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1044000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>926000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>906000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1226000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>922000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>908000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>921000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>954000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>760000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>941000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>833000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>688000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>714000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>538000</v>
+      </c>
+      <c r="E44" s="3">
         <v>533000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>534000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>519000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>527000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>505000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>511000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>500000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>474000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>439000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>438000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>434000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>420000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>412000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>406000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>416000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>405000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>387000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>382000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>363000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>364000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>348000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>331000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>312000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>282000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>261000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>252000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>247000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>242000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>229000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>235000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>237000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>239000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3264000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2558000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4344000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3389000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3034000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2887000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4146000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3344000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3987000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3511000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3546000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3296000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3283000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3480000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3117000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2827000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2663000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3062000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2846000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2285000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2222000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2541000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2426000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2451000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>971000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7155000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7444000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8512000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7878000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6811000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7235000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7416000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7210000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7070000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6441000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5653000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5273000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5491000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6028000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4921000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5328000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5061000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5855000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4796000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4911000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3560000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4662000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3936000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3999000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E47" s="3">
         <v>50000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>71000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>62000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>81000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>72000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>64000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4470000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4378000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4332000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4818000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5118000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4999000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5040000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4897000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4961000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4735000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4650000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4341000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4626000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4568000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4504000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4367000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>60310000</v>
+      </c>
+      <c r="E48" s="3">
         <v>59478000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>58550000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>57894000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57183000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>56346000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55557000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55516000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54928000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54129000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>53446000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52849000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52632000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>51286000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50036000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49355000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>48927000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>47582000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>46225000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45503000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>44978000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43940000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>43156000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>42697000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9171000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9117000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9027000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8959000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8813000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7728000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7885000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7913000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11573000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11761000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11614000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11780000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11504000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10710000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11165000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10925000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10423000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10384000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11380000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11271000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11218000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11042000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7925000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7730000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>85579000</v>
+      </c>
+      <c r="E54" s="3">
         <v>84749000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84818000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>83599000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81758000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>80164000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>79551000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>78854000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78041000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76709000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75045000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74720000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>74745000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>73023000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>71162000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70505000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>69372000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>68556000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67051000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66026000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>64382000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64212000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>59521000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58793000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2185000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1892000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1904000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1983000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2108000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1790000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1795000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2359000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2348000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2080000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1973000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2002000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2039000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1797000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1602000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1980000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1691000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1657000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1454000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1752000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1663000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1578000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1366000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>844000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3171000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3240000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3328000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2990000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3894000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4123000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4365000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4279000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4629000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5186000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4160000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3166000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3431000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3818000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3236000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3429000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3427000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2780000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1504000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2176000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1029000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1479000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1692000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>799000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>182000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>779000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>549000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2846000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2630000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2611000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2573000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2721000</v>
-      </c>
       <c r="H59" s="3">
+        <v>2331000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2796000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2672000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2292000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3359000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3286000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3022000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3203000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3176000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3105000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2782000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4466000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4870000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4145000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2738000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2618000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2742000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2861000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2395000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2998000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8439000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8507000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8274000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7907000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8598000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9027000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8827000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8366000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10347000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10820000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9262000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8342000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8609000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8962000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7815000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9497000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10277000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8616000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5899000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6248000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5523000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6003000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5665000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5375000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34590000</v>
+      </c>
+      <c r="E61" s="3">
         <v>33359000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34175000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33663000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31417000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>30645000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30346000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30368000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27025000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25145000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25143000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24967000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24170000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23342000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22891000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20165000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>19632000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18958000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19238000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19125000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>17864000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17066000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>15883000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15683000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AH61" s="3">
         <v>11662000</v>
       </c>
       <c r="AI61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13052000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13540000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13361000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13460000</v>
       </c>
-      <c r="G62" s="3">
-        <v>12482000</v>
-      </c>
       <c r="H62" s="3">
+        <v>12837000</v>
+      </c>
+      <c r="I62" s="3">
         <v>12443000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12269000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12642000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23147000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23451000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22965000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23779000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24177000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23977000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23143000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23620000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23514000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25333000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25468000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25109000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25499000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25790000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25060000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25016000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67839000</v>
+      </c>
+      <c r="E66" s="3">
         <v>66642000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66950000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>65984000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>63814000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>62593000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>61857000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61305000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62420000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61317000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59271000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58989000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58857000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58182000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55750000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55183000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55324000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>54808000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>52798000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>52675000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>48886000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48859000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>46608000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46074000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6529,13 +6696,13 @@
         <v>1645000</v>
       </c>
       <c r="F70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="G70" s="3">
         <v>1654000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1978000</v>
       </c>
       <c r="I70" s="3">
         <v>1978000</v>
@@ -6547,7 +6714,7 @@
         <v>1978000</v>
       </c>
       <c r="L70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="M70" s="3">
         <v>1977000</v>
@@ -6559,17 +6726,17 @@
         <v>1977000</v>
       </c>
       <c r="P70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="Q70" s="3">
         <v>1235000</v>
       </c>
       <c r="R70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="S70" s="3">
         <v>1237000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -6580,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>2193000</v>
@@ -6607,13 +6774,13 @@
         <v>2193000</v>
       </c>
       <c r="AF70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AG70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AI70" s="3">
         <v>2191000</v>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AK70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7567000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7486000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7326000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7166000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7499000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7399000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7553000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7456000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7454000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>7716000</v>
       </c>
       <c r="N72" s="3">
         <v>7716000</v>
       </c>
       <c r="O72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="P72" s="3">
         <v>7894000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7636000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8229000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8163000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8155000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7881000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8410000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8333000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8382000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8469000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8222000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8034000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13920000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14018000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13779000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13518000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13828000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13692000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13815000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13670000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13643000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13415000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13797000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13754000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13911000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13606000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14177000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14085000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14048000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13748000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14253000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13351000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13303000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13160000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10720000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10526000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E81" s="3">
         <v>516000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>439000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>378000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>155000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>354000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>310000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>415000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-101000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>241000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>110000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>523000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-341000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>318000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>259000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>526000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-288000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>318000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>183000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>143000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>471000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>392000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>278000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>513000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>276000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>218000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>470000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>278000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>362000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>346000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E83" s="3">
         <v>663000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>695000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>676000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>312000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>761000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>592000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>624000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>656000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>761000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>592000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>624000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>579000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>619000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>548000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>542000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>517000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>507000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>504000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>501000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>487000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>479000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>339000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>498000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>301000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>565000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>595000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>479000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>524000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>543000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>528000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>520000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>523000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1170000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2472000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>329000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1043000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>855000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1834000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>802000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-90000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1104000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>874000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>446000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>792000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>427000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>958000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>72000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>192000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>446000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>310000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>315000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>510000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>388000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>210000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>906000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>401000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>816000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>899000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>554000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>884000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>754000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1496000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1511000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1439000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1427000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-986000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,46 +9052,47 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E96" s="3">
         <v>301000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>300000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>295000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>279000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>278000</v>
       </c>
       <c r="I96" s="3">
         <v>278000</v>
       </c>
       <c r="J96" s="3">
+        <v>278000</v>
+      </c>
+      <c r="K96" s="3">
         <v>277000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-263000</v>
       </c>
       <c r="L96" s="3">
         <v>-263000</v>
       </c>
       <c r="M96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="N96" s="3">
         <v>-262000</v>
       </c>
       <c r="O96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="P96" s="3">
         <v>-247000</v>
@@ -8871,31 +9104,31 @@
         <v>-247000</v>
       </c>
       <c r="S96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="T96" s="3">
         <v>-237000</v>
       </c>
       <c r="U96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-228000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-226000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-216000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-195000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-199000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AB96" s="3">
         <v>-197000</v>
@@ -8907,25 +9140,28 @@
         <v>-197000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AH96" s="3">
         <v>-177000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9478,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1201000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>577000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>988000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>567000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-339000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-97000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1316000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1049000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>713000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>914000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>205000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>939000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>724000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2271000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1511000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1080000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>424000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2231000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>345000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2907000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>642000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1009000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>393000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>491000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>111000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>112000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>195000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-156000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-488000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>755000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>251000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-640000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-79000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>684000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>110000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-111000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-160000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-131000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>440000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-305000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>301000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-432000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-812000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1268000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-478000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>283000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-120000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>233000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>73000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>997000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>19000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>55000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3811000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3984000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5201000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4336000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4078000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3706000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4702000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3964000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3966000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4016000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5228000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4008000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3968000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3331000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5299000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3315000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2960000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3157000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4644000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2987000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2790000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2970000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3741000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2812000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2824000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2030000</v>
+      </c>
+      <c r="E9" s="3">
         <v>361000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3244000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2519000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2325000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>-872000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2870000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2388000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2402000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2446000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3464000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2665000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2524000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1984000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3310000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2037000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1857000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1843000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3065000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1830000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1809000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1691000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2549000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1730000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1887000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1781000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3623000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1957000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1817000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1753000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4578000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1832000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1576000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1564000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1570000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1764000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1343000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1444000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1347000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1989000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1278000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1103000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1314000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1579000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1157000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>981000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1279000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1192000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1082000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>937000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>984000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>963000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,16 +1179,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>416000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1183,11 +1197,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>358000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,222 +1397,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1255000</v>
+      </c>
+      <c r="E14" s="3">
         <v>79000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>84000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>37000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>651000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>144000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>536000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>53000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>151000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>45000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>942000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>118000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>478000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>58000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1405000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>43000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>53000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>39000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1354000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>65000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>84000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>425000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>170000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>66000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>716000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>16000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>742000</v>
+      </c>
+      <c r="E15" s="3">
         <v>728000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>710000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>726000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>702000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>664000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>665000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>650000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>656000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>639000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>738000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>601000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>583000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>561000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>599000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>533000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>525000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>504000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>490000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>489000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>484000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>470000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>459000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>321000</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>480000</v>
       </c>
       <c r="AB15" s="3">
         <v>480000</v>
       </c>
       <c r="AC15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>466000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>463000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>462000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>506000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>524000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>512000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>499000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>503000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,115 +1656,119 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2917000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3090000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4100000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3377000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3160000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2749000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3648000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3161000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3172000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3252000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5272000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3504000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3709000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2710000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5427000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2730000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2561000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2363000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5023000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2487000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2488000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2683000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3105000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2312000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2472000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1746,106 +1776,109 @@
         <v>894000</v>
       </c>
       <c r="E18" s="3">
+        <v>894000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1101000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>959000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>918000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>957000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1054000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>803000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>794000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>764000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-44000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>504000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>259000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>621000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-128000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>585000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>399000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>794000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-379000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>500000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>302000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>287000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>636000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>500000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>352000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>739000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>420000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>330000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>553000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>470000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>471000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>567000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-40000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-53000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-49000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-33000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-35000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>129000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>85000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>66000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>68000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>42000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>47000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>76000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>72000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>34000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>84000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>81000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>42000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>58000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>55000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>38000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>76000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>49000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>51000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>34000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>41000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>24000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>11000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1632000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1851000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1738000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1669000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1654000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1753000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1488000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1484000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1549000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>802000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1162000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>951000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1242000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>538000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1209000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1013000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1345000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>212000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1085000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>855000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>816000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1173000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>894000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>888000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>860000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>520000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E22" s="3">
         <v>468000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>477000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>480000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>444000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>426000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>433000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>392000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>361000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>350000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>302000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>271000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>246000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>231000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>245000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>232000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>217000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>226000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>222000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>229000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>225000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>222000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>214000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>211000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>194000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>196000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>188000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>180000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>170000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>166000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>162000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>159000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>152000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>150000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1884000</v>
+      </c>
+      <c r="E23" s="3">
         <v>343000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>584000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>498000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-124000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>445000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>132000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>405000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>323000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>543000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-261000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>299000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>81000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>432000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-326000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>429000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>254000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>602000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-517000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>352000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>129000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>107000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>480000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>344000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>196000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>627000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>289000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>211000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>432000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>335000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>352000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>428000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>448000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>68000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>59000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-113000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>67000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-23000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>51000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-187000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-55000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-139000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-29000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>68000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-36000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-275000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-84000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-78000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>83000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>26000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>64000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E26" s="3">
         <v>340000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>516000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>439000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>378000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>155000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>354000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>310000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>470000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-74000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>292000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>136000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>571000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-297000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>361000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>290000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>552000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-242000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>348000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>213000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>173000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>502000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>422000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>308000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>544000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>298000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>242000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>501000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>309000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>392000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>364000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1435000</v>
+      </c>
+      <c r="E27" s="3">
         <v>340000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>516000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>439000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>378000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>155000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>354000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>310000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>415000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-101000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>241000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>110000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>523000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-341000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>318000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>259000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>526000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-288000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>318000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>183000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>143000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>471000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>392000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>278000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>513000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>276000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>218000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>470000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>278000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>333000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2905,17 +2966,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2923,11 +2984,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2935,12 +2996,12 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
@@ -2948,13 +3009,16 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>13000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E32" s="3">
         <v>10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>40000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>53000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>49000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>33000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>35000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-129000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-85000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-66000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-68000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-47000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-76000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-72000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-34000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-84000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-81000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E33" s="3">
         <v>340000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>516000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>439000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>378000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>155000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>354000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>310000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>415000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>241000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>110000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>523000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-341000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>318000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>259000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>526000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-288000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>318000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>183000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>143000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>471000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>392000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>278000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>513000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>276000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>218000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>470000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>278000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>346000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E35" s="3">
         <v>340000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>516000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>439000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>378000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>155000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>354000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>310000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>415000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>241000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>110000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>523000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-341000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>318000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>259000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>526000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-288000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>318000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>183000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>143000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>471000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>392000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>278000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>513000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>276000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>218000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>470000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>278000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>346000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1318000</v>
+      </c>
+      <c r="E41" s="3">
         <v>193000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>465000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>992000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>446000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>195000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>836000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>914000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>232000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>122000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>231000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>390000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>524000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>389000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>87000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>92000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>524000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1337000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>68000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>547000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>257000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>328000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>144000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>71000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>99000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>105000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>117000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>98000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>150000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>96000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,650 +4089,671 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2669000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3017000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3982000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3027000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2667000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2758000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3292000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2473000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2217000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1695000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2259000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1547000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1312000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1398000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1612000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1314000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1696000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1906000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2314000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1044000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>926000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>906000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1226000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>922000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>908000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>921000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>954000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>760000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>941000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>833000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>688000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>714000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>539000</v>
+      </c>
+      <c r="E44" s="3">
         <v>538000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>533000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>534000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>519000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>527000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>505000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>511000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>500000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>474000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>439000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>438000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>434000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>420000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>412000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>406000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>416000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>405000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>387000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>382000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>363000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>364000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>348000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>331000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>312000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>282000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>261000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>252000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>247000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>242000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>229000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>235000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>237000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>239000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2579000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3264000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2558000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4344000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3389000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3034000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2887000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4146000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3344000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3987000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3511000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3546000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3296000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3283000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3480000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3117000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2827000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2663000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3062000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2846000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2285000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2222000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2541000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2426000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2451000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>971000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7427000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7155000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7444000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8512000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7878000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6811000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7235000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7416000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7210000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7070000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6441000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5653000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5273000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5491000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6028000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4921000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5328000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5061000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5855000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4796000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4911000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3560000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4662000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3936000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3999000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E47" s="3">
         <v>57000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>71000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>62000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>81000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>72000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>64000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4470000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4378000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4332000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4818000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5118000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4999000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5040000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4897000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4961000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4735000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4650000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4341000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4626000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4568000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4504000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4367000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>61323000</v>
+      </c>
+      <c r="E48" s="3">
         <v>60310000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>59478000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>58550000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57894000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57183000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>56346000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55557000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55516000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54928000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54129000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>53446000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52849000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>52632000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51286000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50036000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49355000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>48927000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>47582000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>46225000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>45503000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>44978000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>43940000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>43156000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42697000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9063000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9171000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9117000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9027000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8959000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8813000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7728000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7885000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7913000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11573000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11761000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11614000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11780000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11504000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10710000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11165000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10925000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10423000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10384000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11380000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11271000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11218000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11042000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7925000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7730000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88420000</v>
+      </c>
+      <c r="E54" s="3">
         <v>85579000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84749000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84818000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>83599000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>81758000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>80164000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>79551000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78854000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78041000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76709000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>75045000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>74720000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74745000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>73023000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>71162000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>70505000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>69372000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>68556000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>67051000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66026000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>64382000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64212000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59521000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>58793000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2156000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2185000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1892000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1904000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1983000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2108000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1790000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1795000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2359000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2348000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2080000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1973000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2002000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2039000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1797000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1602000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1980000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1691000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1657000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1454000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1752000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1663000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1578000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1366000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>844000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3127000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3171000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3240000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3328000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2990000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3894000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4123000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4365000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4279000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4629000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5186000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4160000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3166000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3431000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3818000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3236000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3429000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3427000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2780000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1504000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2176000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1029000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1479000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1692000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>799000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>182000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>779000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>549000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1991000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2846000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2630000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2611000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2573000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2331000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2796000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2672000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2292000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3359000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3286000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3022000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3203000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3176000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3105000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2782000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4466000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4870000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4145000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2738000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2618000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2742000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2861000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2395000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2998000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7769000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8439000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8507000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8274000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7907000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8598000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9027000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8827000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8366000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10347000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10820000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9262000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8342000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8609000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8962000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7815000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9497000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10277000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8616000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5899000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6248000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5523000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6003000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5665000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5375000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36433000</v>
+      </c>
+      <c r="E61" s="3">
         <v>34590000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33359000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34175000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33663000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31417000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>30645000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30346000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30368000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27025000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25145000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25143000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24967000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24170000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23342000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22891000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>20165000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>19632000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18958000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19238000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19125000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17864000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17066000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15883000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15683000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AI61" s="3">
         <v>11662000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13132000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13052000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13540000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13361000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13460000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12837000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12443000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12269000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12642000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23147000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23451000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22965000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23779000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24177000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23977000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23143000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23620000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23514000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25333000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25468000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25109000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25499000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25790000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25060000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25016000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69623000</v>
+      </c>
+      <c r="E66" s="3">
         <v>67839000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66642000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66950000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>65984000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63814000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>62593000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61857000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61305000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62420000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61317000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>59271000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>58989000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58857000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>58182000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55750000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55183000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55324000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54808000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>52798000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>52675000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48886000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48859000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>46608000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46074000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6699,13 +6867,13 @@
         <v>1645000</v>
       </c>
       <c r="G70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="H70" s="3">
         <v>1654000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="I70" s="3">
-        <v>1978000</v>
       </c>
       <c r="J70" s="3">
         <v>1978000</v>
@@ -6717,7 +6885,7 @@
         <v>1978000</v>
       </c>
       <c r="M70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="N70" s="3">
         <v>1977000</v>
@@ -6729,17 +6897,17 @@
         <v>1977000</v>
       </c>
       <c r="Q70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="R70" s="3">
         <v>1235000</v>
       </c>
       <c r="S70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="T70" s="3">
         <v>1237000</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -6750,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>2193000</v>
@@ -6777,13 +6945,13 @@
         <v>2193000</v>
       </c>
       <c r="AG70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AH70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AJ70" s="3">
         <v>2191000</v>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AL70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8662000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7567000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7486000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7326000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7166000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7499000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7399000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7553000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7456000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7454000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="N72" s="3">
-        <v>7716000</v>
       </c>
       <c r="O72" s="3">
         <v>7716000</v>
       </c>
       <c r="P72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="Q72" s="3">
         <v>7894000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7636000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8229000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8163000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8155000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7881000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8410000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8333000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8382000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8469000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8222000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8034000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14977000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13920000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14018000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13779000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13518000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13828000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13692000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13815000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13670000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13643000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13415000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13797000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13754000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13911000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13606000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14177000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14085000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14048000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13748000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14253000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13351000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13303000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13160000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10720000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10526000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E81" s="3">
         <v>340000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>516000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>439000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>378000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>155000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>354000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>310000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>415000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>241000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>110000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>523000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-341000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>318000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>259000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>526000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-288000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>318000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>183000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>143000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>471000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>392000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>278000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>513000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>276000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>218000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>470000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>278000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>346000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>707000</v>
+      </c>
+      <c r="E83" s="3">
         <v>329000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>663000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>695000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>676000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>312000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>761000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>592000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>624000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>656000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>761000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>592000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>624000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>579000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>619000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>548000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>542000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>517000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>507000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>504000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>501000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>487000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>479000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>339000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>498000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>301000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>565000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>595000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>479000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>524000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>543000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>528000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>523000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1224000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1170000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2472000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>329000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1043000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>855000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1834000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>802000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-90000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1104000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>874000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>446000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>792000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>427000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>958000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>72000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>192000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>446000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>310000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>315000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>510000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>388000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>210000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>906000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>401000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>816000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>899000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>554000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>884000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>754000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1408000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1496000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1511000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1374000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1439000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1427000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-986000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,49 +9286,50 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E96" s="3">
         <v>302000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>301000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>300000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>295000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>279000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>278000</v>
       </c>
       <c r="J96" s="3">
         <v>278000</v>
       </c>
       <c r="K96" s="3">
+        <v>278000</v>
+      </c>
+      <c r="L96" s="3">
         <v>277000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-263000</v>
       </c>
       <c r="M96" s="3">
         <v>-263000</v>
       </c>
       <c r="N96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="O96" s="3">
         <v>-262000</v>
       </c>
       <c r="P96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="Q96" s="3">
         <v>-247000</v>
@@ -9107,31 +9341,31 @@
         <v>-247000</v>
       </c>
       <c r="T96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="U96" s="3">
         <v>-237000</v>
       </c>
       <c r="V96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-228000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-226000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-216000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-195000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AC96" s="3">
         <v>-197000</v>
@@ -9143,25 +9377,28 @@
         <v>-197000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AI96" s="3">
         <v>-177000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,115 +9724,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="E100" s="3">
         <v>310000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1201000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>577000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>988000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>567000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-339000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-97000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1316000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1049000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>713000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>914000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>205000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>939000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>724000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2271000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1511000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1080000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>424000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2231000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>345000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2907000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>642000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1009000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>393000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>491000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>111000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>112000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>195000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1224000</v>
+      </c>
+      <c r="E102" s="3">
         <v>41000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-156000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-488000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>755000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>83000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>251000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-640000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-79000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>684000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>110000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-111000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-160000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-131000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>440000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-305000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>301000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-432000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-812000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1268000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-478000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>283000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-120000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>233000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>73000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>997000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>19000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>12000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4543000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3811000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3984000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5201000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4336000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4078000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3706000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4702000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3964000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3966000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4016000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5228000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4008000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3968000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3331000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5299000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3315000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2960000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3157000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4644000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2987000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2790000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2970000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3741000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2812000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2824000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2737000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2030000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>361000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3244000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2519000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2325000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>-872000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2870000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2388000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2402000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2446000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3464000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2665000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2524000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1984000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3310000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2037000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1857000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1843000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3065000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1830000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1809000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1691000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2549000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1730000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1887000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1781000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3623000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1957000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1817000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1753000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4578000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1832000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1576000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1564000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1570000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1764000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1343000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1347000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1989000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1278000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1103000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1314000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1579000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1157000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>981000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1279000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1082000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>937000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>984000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>963000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,19 +1193,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>416000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1200,11 +1214,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>358000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,228 +1417,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1255000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>79000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>84000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>37000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>651000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>144000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>536000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>53000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>151000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>45000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>942000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>118000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>478000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>58000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1405000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>43000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>53000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>39000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1354000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>65000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>84000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>425000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>170000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>66000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>716000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5000</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E15" s="3">
         <v>742000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>728000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>710000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>726000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>702000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>664000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>665000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>650000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>656000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>639000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>738000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>601000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>583000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>561000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>599000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>533000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>525000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>504000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>490000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>489000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>484000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>470000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>459000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>321000</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>480000</v>
       </c>
       <c r="AC15" s="3">
         <v>480000</v>
       </c>
       <c r="AD15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AE15" s="3">
         <v>466000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>463000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>462000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>506000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>524000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>512000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>499000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>503000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3711000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2917000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3090000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4100000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3377000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3160000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2749000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3648000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3161000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3172000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3252000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5272000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3504000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3709000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2710000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5427000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2730000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2561000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2363000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5023000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2487000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2488000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2683000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3105000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2312000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2472000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>894000</v>
+        <v>832000</v>
       </c>
       <c r="E18" s="3">
         <v>894000</v>
       </c>
       <c r="F18" s="3">
+        <v>894000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1101000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>959000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>918000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>957000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1054000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>803000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>794000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>764000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-44000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>504000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>259000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>621000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-128000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>585000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>399000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>794000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-379000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>500000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>302000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>287000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>636000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>500000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>352000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>739000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>420000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>330000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>553000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>470000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>471000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>567000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-47000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-40000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-53000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-49000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-33000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-35000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>129000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>85000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>66000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>68000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>42000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>47000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>76000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>72000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>34000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>84000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>81000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>52000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>42000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>58000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>55000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>38000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>21000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>76000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>49000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>51000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>34000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>41000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>33000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>11000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1716000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1683000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1632000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1851000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1738000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1669000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1654000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1753000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1488000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1484000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1549000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>802000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1162000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>951000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1242000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>538000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1209000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1013000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1345000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>212000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1085000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>855000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>816000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1173000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>894000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>888000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>860000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>520000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E22" s="3">
         <v>301000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>468000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>477000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>480000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>444000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>426000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>433000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>392000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>361000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>350000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>302000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>271000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>246000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>231000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>245000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>232000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>217000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>226000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>222000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>229000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>225000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>222000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>214000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>211000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>194000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>196000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>188000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>180000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>170000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>166000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>162000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>159000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>152000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>150000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1884000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>343000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>584000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>498000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-124000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>445000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>132000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>405000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>323000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>543000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-261000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>299000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>81000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>432000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-326000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>429000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>254000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>602000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-517000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>352000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>129000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>107000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>480000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>344000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>196000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>627000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>289000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>211000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>432000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>335000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>352000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>428000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>448000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>59000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-113000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-23000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>73000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-187000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-139000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-29000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>68000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-36000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-275000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-78000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>83000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>64000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1436000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>340000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>516000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>439000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>378000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>155000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>354000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>310000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>470000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-74000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>292000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>136000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>571000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-297000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>361000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>290000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>552000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-242000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>348000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>213000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>173000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>502000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>422000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>308000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>544000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>298000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>242000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>501000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>309000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>392000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>364000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1435000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>340000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>516000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>439000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>378000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>155000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>354000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>310000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>415000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-101000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>241000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>110000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>523000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-341000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>318000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>259000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>526000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-288000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>318000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>183000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>143000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>471000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>392000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>278000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>513000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>276000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>218000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>470000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>362000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>333000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2969,17 +3030,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2987,11 +3048,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2999,12 +3060,12 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
@@ -3012,13 +3073,16 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>13000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E32" s="3">
         <v>47000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>40000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>53000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>49000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>33000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>35000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-129000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-85000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-66000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-42000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-47000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-76000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-72000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-34000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-84000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-81000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-52000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1436000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>340000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>516000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>439000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>378000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>155000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>354000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>310000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>415000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-101000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>241000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>110000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>523000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-341000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>318000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>259000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>526000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-288000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>318000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>183000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>143000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>471000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>392000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>278000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>513000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>276000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>218000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>470000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>362000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>346000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1436000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>340000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>516000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>439000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>378000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>155000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>354000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>310000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>415000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-101000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>241000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>110000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>523000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-341000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>318000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>259000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>526000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-288000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>318000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>183000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>143000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>471000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>392000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>278000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>513000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>276000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>218000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>470000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>362000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>346000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1318000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>193000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>465000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>992000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>446000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>195000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>836000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>914000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>232000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>122000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>231000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>390000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>524000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>84000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>389000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>87000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>92000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>524000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1337000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>547000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>257000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>328000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>144000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>71000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>99000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>105000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>117000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>98000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>150000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>96000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,668 +4182,689 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2829000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2669000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3017000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3982000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3027000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2667000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2758000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3292000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2473000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2217000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1695000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2259000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1547000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1398000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1612000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1314000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1696000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1906000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2314000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1044000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>926000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>906000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1226000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>922000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>908000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>921000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>954000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>760000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>941000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>833000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>688000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>714000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>523000</v>
+      </c>
+      <c r="E44" s="3">
         <v>539000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>538000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>533000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>534000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>519000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>527000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>505000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>511000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>500000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>474000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>439000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>438000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>434000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>420000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>412000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>406000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>416000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>405000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>387000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>382000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>363000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>364000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>348000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>331000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>312000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>282000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>261000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>252000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>247000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>242000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>229000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>235000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>237000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>239000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3332000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2579000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3264000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2558000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4344000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3389000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3034000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2887000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4146000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3344000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3987000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3511000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3546000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3296000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3283000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3480000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3117000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2827000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2663000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3062000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2846000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2285000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2222000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2541000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2426000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2451000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>971000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6950000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7427000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7155000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7444000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8512000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7878000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6811000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7235000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7416000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7210000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7070000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6441000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5653000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5273000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5491000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6028000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4921000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5328000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5061000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5855000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4796000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4911000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3560000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4662000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3936000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3999000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E47" s="3">
         <v>59000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>57000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>62000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>81000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>72000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>64000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4470000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4378000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4332000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4818000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5118000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4999000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5040000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4897000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4961000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4735000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4650000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4341000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4626000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4568000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4504000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4367000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62155000</v>
+      </c>
+      <c r="E48" s="3">
         <v>61323000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>60310000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>59478000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>58550000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57894000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57183000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>56346000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55557000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55516000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54928000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>54129000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>53446000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>52849000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>52632000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>51286000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50036000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>49355000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>48927000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>47582000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>46225000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>45503000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>44978000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>43940000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>43156000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42697000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>0</v>
       </c>
+      <c r="AM49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9158000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9063000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9171000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9117000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9027000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8959000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8813000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7728000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7885000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7913000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11573000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11761000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11614000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11780000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11504000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10710000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11165000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10925000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10423000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10384000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11380000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11271000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11218000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11042000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7925000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7730000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88813000</v>
+      </c>
+      <c r="E54" s="3">
         <v>88420000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85579000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>84749000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>84818000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>83599000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>81758000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>80164000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>79551000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78854000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>78041000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76709000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>75045000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74720000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>74745000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>73023000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>71162000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>70505000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>69372000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>68556000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>67051000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66026000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>64382000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64212000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59521000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>58793000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1962000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2156000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2185000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1892000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1904000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1983000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2108000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1790000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1795000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2359000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2348000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2080000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1973000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2002000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2039000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1797000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1602000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1980000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1691000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1657000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1454000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1752000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1663000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1578000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1366000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>844000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3519000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3127000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3171000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3240000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3328000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2990000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3894000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4123000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4365000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4279000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4629000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5186000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4160000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3166000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3431000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3818000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3236000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3429000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3427000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2780000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1504000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2176000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1029000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1479000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1692000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>799000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>182000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>779000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>549000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1991000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2846000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2630000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2611000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2573000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2331000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2796000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2672000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2292000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3359000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3286000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3022000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3203000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3176000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3105000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2782000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4466000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4870000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4145000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2738000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2618000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2742000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2861000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2395000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2998000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7965000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7769000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8439000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8507000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8274000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7907000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8598000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9027000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8827000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8366000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10347000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10820000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9262000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8342000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8609000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8962000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7815000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9497000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10277000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8616000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5899000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6248000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5523000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6003000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5665000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5375000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36007000</v>
+      </c>
+      <c r="E61" s="3">
         <v>36433000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>34590000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33359000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34175000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33663000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31417000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>30645000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30346000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30368000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27025000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25145000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>25143000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24967000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>24170000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23342000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22891000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20165000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>19632000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18958000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19238000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19125000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>17864000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>17066000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15883000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15683000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AI61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AJ61" s="3">
         <v>11662000</v>
       </c>
       <c r="AK61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AL61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13132000</v>
+        <v>13885000</v>
       </c>
       <c r="E62" s="3">
+        <v>13470000</v>
+      </c>
+      <c r="F62" s="3">
         <v>13052000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13540000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13361000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13460000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12837000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12443000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12269000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12642000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23147000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23451000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22965000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23779000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>24177000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23977000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23143000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23620000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23514000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25333000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25468000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25109000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25499000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25790000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25060000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25016000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69952000</v>
+      </c>
+      <c r="E66" s="3">
         <v>69623000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>67839000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66642000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66950000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65984000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63814000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>62593000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>61857000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>61305000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62420000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61317000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59271000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58989000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>58857000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58182000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55750000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>55183000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55324000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>54808000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>52798000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>52675000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48886000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48859000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46608000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46074000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6870,13 +7038,13 @@
         <v>1645000</v>
       </c>
       <c r="H70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="I70" s="3">
         <v>1654000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>1978000</v>
       </c>
       <c r="K70" s="3">
         <v>1978000</v>
@@ -6888,7 +7056,7 @@
         <v>1978000</v>
       </c>
       <c r="N70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="O70" s="3">
         <v>1977000</v>
@@ -6900,17 +7068,17 @@
         <v>1977000</v>
       </c>
       <c r="R70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="S70" s="3">
         <v>1235000</v>
       </c>
       <c r="T70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="U70" s="3">
         <v>1237000</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -6921,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="Z70" s="3">
         <v>2193000</v>
@@ -6948,13 +7116,13 @@
         <v>2193000</v>
       </c>
       <c r="AH70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AI70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AJ70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AK70" s="3">
         <v>2191000</v>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AM70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8709000</v>
+      </c>
+      <c r="E72" s="3">
         <v>8662000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7567000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7486000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7326000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7166000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7499000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7399000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7553000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7456000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7454000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>7716000</v>
       </c>
       <c r="P72" s="3">
         <v>7716000</v>
       </c>
       <c r="Q72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="R72" s="3">
         <v>7894000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7636000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8229000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8163000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8155000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7881000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8410000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8333000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8382000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8469000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8222000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8034000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15041000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14977000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13920000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14018000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13779000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13518000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13828000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13692000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13815000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13670000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13643000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13415000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13797000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13754000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13911000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13606000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14177000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14085000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14048000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13748000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14253000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13351000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13303000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13160000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10720000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10526000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1436000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>340000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>516000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>439000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>378000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>155000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>354000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>310000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>415000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-101000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>241000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>110000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>523000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-341000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>318000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>259000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>526000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-288000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>318000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>183000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>143000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>471000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>392000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>278000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>513000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>276000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>218000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>470000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>362000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>346000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E83" s="3">
         <v>707000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>329000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>663000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>695000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>676000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>312000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>761000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>592000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>624000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>656000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>761000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>592000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>624000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>579000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>619000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>548000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>542000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>517000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>507000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>504000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>501000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>487000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>479000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>339000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>498000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>301000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>565000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>595000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>479000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>524000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>543000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>528000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>520000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>523000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>882000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1224000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1170000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2472000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>329000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1043000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>855000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1834000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>802000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-90000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1104000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>874000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>446000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>792000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>427000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>958000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>72000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>192000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>446000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>310000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>315000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>510000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>388000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>210000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>906000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>401000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>816000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>899000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>554000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>884000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>754000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1712000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1408000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1496000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1511000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1628000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1374000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1439000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1427000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-986000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,52 +9520,53 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E96" s="3">
         <v>319000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>302000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>301000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>300000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>295000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>279000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>278000</v>
       </c>
       <c r="K96" s="3">
         <v>278000</v>
       </c>
       <c r="L96" s="3">
+        <v>278000</v>
+      </c>
+      <c r="M96" s="3">
         <v>277000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-263000</v>
       </c>
       <c r="N96" s="3">
         <v>-263000</v>
       </c>
       <c r="O96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="P96" s="3">
         <v>-262000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="R96" s="3">
         <v>-247000</v>
@@ -9344,31 +9578,31 @@
         <v>-247000</v>
       </c>
       <c r="U96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="V96" s="3">
         <v>-237000</v>
       </c>
       <c r="W96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-228000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-226000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-216000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AD96" s="3">
         <v>-197000</v>
@@ -9380,25 +9614,28 @@
         <v>-197000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-177000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-383000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1374000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>310000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1201000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>577000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>988000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>567000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-339000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-97000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1316000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1049000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>713000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>914000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>205000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>939000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>724000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2271000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1511000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1080000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>424000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>345000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2907000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>642000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1009000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>393000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>491000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>112000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>195000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1129000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1224000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>41000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-156000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-488000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>755000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>83000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>251000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-640000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-79000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>684000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>110000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-111000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-131000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>440000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-305000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>301000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-432000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-812000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1268000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-478000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>283000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-120000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>233000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>73000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>997000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>19000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>55000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>12000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5213000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5750000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4543000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3811000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3984000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5201000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4336000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4078000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3706000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4702000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3964000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3966000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4016000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5228000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4008000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3968000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3331000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5299000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3315000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2960000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3157000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4644000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2987000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2790000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2970000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3741000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2812000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2824000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>503000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2876000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2737000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2030000</v>
       </c>
-      <c r="G9" s="3">
-        <v>361000</v>
-      </c>
       <c r="H9" s="3">
-        <v>3291000</v>
+        <v>358000</v>
       </c>
       <c r="I9" s="3">
+        <v>3247000</v>
+      </c>
+      <c r="J9" s="3">
         <v>2519000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2325000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>-872000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2870000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2388000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2402000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2446000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3464000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2665000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2524000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1984000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3310000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2037000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1857000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1843000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3065000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1830000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1809000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1691000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2549000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1730000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1887000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4710000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2874000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1806000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1781000</v>
       </c>
-      <c r="G10" s="3">
-        <v>3623000</v>
-      </c>
       <c r="H10" s="3">
-        <v>1910000</v>
+        <v>3626000</v>
       </c>
       <c r="I10" s="3">
+        <v>1954000</v>
+      </c>
+      <c r="J10" s="3">
         <v>1817000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1753000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4578000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1832000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1576000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1564000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1570000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1764000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1343000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1444000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1347000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1989000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1278000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1103000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1314000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1579000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1157000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>981000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1279000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1082000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>937000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>984000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>963000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,13 +1220,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>463000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1222,11 +1235,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>416000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1234,11 +1247,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>358000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,240 +1456,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-904000</v>
+      </c>
+      <c r="E14" s="3">
         <v>421000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1255000</v>
       </c>
-      <c r="G14" s="3">
-        <v>79000</v>
-      </c>
       <c r="H14" s="3">
+        <v>82000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>81000</v>
+      </c>
+      <c r="J14" s="3">
         <v>37000</v>
       </c>
-      <c r="I14" s="3">
-        <v>37000</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>651000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>144000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>536000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>53000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>151000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>45000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>942000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>118000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>478000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>58000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1405000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>43000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>53000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>39000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1354000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>65000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>84000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>425000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>170000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>66000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>716000</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>16000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>5000</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>807000</v>
+      </c>
+      <c r="E15" s="3">
         <v>862000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>826000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>742000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>728000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>710000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>726000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>702000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>664000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>665000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>650000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>656000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>639000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>738000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>601000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>583000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>561000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>599000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>533000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>525000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>504000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>490000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>489000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>484000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>470000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>459000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>321000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>480000</v>
       </c>
       <c r="AE15" s="3">
         <v>480000</v>
       </c>
       <c r="AF15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>466000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>463000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>462000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>506000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>524000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>512000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>499000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>503000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3339000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3878000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3711000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2917000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3090000</v>
-      </c>
       <c r="H17" s="3">
-        <v>4147000</v>
+        <v>3087000</v>
       </c>
       <c r="I17" s="3">
+        <v>4103000</v>
+      </c>
+      <c r="J17" s="3">
         <v>3377000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3160000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2749000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3648000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3161000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3172000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3252000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5272000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3504000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3709000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2710000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5427000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2730000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2561000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2363000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5023000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2487000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2488000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2683000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3105000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2312000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2472000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1874000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1872000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>832000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>894000</v>
       </c>
       <c r="G18" s="3">
         <v>894000</v>
       </c>
       <c r="H18" s="3">
+        <v>897000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>959000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>918000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>957000</v>
+      </c>
+      <c r="M18" s="3">
         <v>1054000</v>
       </c>
-      <c r="I18" s="3">
-        <v>959000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>918000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>957000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1054000</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>803000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>794000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>764000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>504000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>259000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>621000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-128000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>585000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>399000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>794000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-379000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>500000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>302000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>287000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>636000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>500000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>352000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>739000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>420000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>330000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>553000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>470000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>471000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>567000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2017,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-46000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-58000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-47000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-40000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-53000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-49000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-33000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-35000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>129000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>85000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>66000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>68000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>42000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>47000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>76000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>72000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>34000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>84000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>81000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>52000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>42000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>58000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>55000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>38000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>21000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>76000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>49000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>51000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>41000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>24000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>33000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>11000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2704000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2780000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1716000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1683000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1632000</v>
-      </c>
       <c r="H21" s="3">
-        <v>1804000</v>
+        <v>1635000</v>
       </c>
       <c r="I21" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1738000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1669000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1654000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1753000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1488000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1484000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1549000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>802000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1162000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>951000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1242000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>538000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1209000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1013000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1345000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>212000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1085000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>855000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>816000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1173000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>894000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>888000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>860000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E22" s="3">
         <v>488000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>504000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>301000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>468000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>477000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>480000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>444000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>426000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>433000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>392000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>361000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>350000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>302000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>271000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>246000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>231000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>245000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>232000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>217000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>226000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>222000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>229000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>225000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>222000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>214000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>211000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>194000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>196000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>188000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>180000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>170000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>166000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>162000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>159000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>152000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>150000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2530000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1007000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>329000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1884000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>343000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>584000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>498000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-124000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>445000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>132000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>405000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>323000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>543000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-261000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>299000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>81000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>432000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-326000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>429000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>254000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>602000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-517000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>352000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>129000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>107000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>480000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>344000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>196000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>627000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>289000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>211000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>432000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>335000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>352000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>428000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>682000</v>
+      </c>
+      <c r="E24" s="3">
         <v>175000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>448000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>59000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-113000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>67000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-23000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>51000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-187000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-55000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-139000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-29000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>68000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-36000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>50000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-275000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-84000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-78000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>83000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>26000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>64000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="E26" s="3">
         <v>832000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>343000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1436000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>340000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>516000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>439000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>378000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>155000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>354000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>310000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>470000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-74000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>292000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>136000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>571000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-297000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>361000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>290000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>552000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-242000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>348000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>213000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>173000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>502000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>422000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>308000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>544000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>298000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>242000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>501000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>309000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>392000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>364000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1846000</v>
+      </c>
+      <c r="E27" s="3">
         <v>832000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>343000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1435000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>340000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>516000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>439000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>378000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>155000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>354000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>310000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>415000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>241000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>110000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>523000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-341000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>318000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>259000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>526000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-288000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>318000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>183000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>143000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>471000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>392000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>278000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>513000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>276000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>218000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>470000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>278000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>362000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>333000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3097,17 +3157,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3115,11 +3175,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3127,12 +3187,12 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
         <v>0</v>
       </c>
@@ -3140,13 +3200,16 @@
         <v>0</v>
       </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>13000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E32" s="3">
         <v>46000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>58000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>47000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>40000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>53000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>49000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>33000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>35000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-129000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-85000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-66000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-68000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-42000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-47000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-76000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-72000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-34000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-84000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-81000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-52000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-58000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="E33" s="3">
         <v>832000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>343000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1436000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>340000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>516000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>439000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>378000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>155000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>354000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>310000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>415000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>241000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>110000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>523000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-341000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>318000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>259000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>526000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-288000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>318000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>183000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>143000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>471000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>392000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>278000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>513000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>276000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>218000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>470000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>278000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>362000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>346000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="E35" s="3">
         <v>832000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>343000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1436000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>340000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>516000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>439000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>378000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>155000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>354000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>310000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>415000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>241000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>110000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>523000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-341000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>318000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>259000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>526000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-288000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>318000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>183000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>143000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>471000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>392000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>278000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>513000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>276000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>218000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>470000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>278000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>362000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>346000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E41" s="3">
         <v>364000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>140000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1318000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>193000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>465000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>992000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>345000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>446000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>195000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>836000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>914000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>232000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>122000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>231000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>390000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>524000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>84000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>389000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>87000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>92000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>524000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1337000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>68000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>547000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>257000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>328000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>144000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>71000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>99000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>105000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>117000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>98000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>150000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>96000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,704 +4367,725 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2701000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3443000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2829000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2669000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3017000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3982000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3027000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2667000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2758000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3292000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2473000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2217000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1695000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2259000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1547000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1312000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1398000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1612000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1314000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1696000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1906000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2314000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1044000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>926000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>906000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1226000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>922000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>908000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>921000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>954000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>760000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>941000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>833000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>688000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>714000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E44" s="3">
         <v>524000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>523000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>539000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>538000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>533000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>534000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>519000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>527000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>505000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>511000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>500000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>474000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>439000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>438000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>434000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>420000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>412000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>406000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>416000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>405000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>387000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>382000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>363000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>364000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>348000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>331000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>312000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>282000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>261000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>252000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>247000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>242000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>229000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>235000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>237000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>239000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3621000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3189000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3332000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2579000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3264000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2558000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4344000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3389000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3034000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2887000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4146000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3344000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3987000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3511000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3546000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3296000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3283000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3480000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3117000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2827000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2663000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3062000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2846000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2285000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2222000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2541000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2426000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2451000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>971000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7686000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7728000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6950000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7427000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7155000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7444000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8512000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7878000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6811000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7235000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7416000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7210000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7070000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6441000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5653000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5273000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5491000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6028000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4921000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5328000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5061000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5855000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4796000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4911000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3560000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4662000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3936000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3999000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E47" s="3">
         <v>70000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>63000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>57000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>71000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>62000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>54000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>81000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>64000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4470000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4378000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4332000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4818000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5118000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4999000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5040000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4897000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4961000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4735000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4650000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4341000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4626000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4568000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4504000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4367000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>64359000</v>
+      </c>
+      <c r="E48" s="3">
         <v>62968000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62155000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61323000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60310000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>59478000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>58550000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57894000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57183000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>56346000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55557000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55516000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>54928000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>54129000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>53446000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>52849000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>52632000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>51286000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>50036000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>49355000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>48927000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>47582000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>46225000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>45503000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>44978000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>43940000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>43156000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>42697000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3">
         <v>0</v>
       </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8970000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9037000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9158000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9063000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9171000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9117000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9027000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8959000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8813000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7728000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7885000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7913000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11573000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11761000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11614000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11780000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11504000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10710000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11165000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10925000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10423000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10384000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11380000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11271000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11218000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11042000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7925000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7730000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94026000</v>
+      </c>
+      <c r="E54" s="3">
         <v>90489000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88813000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>88420000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>85579000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>84749000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84818000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>83599000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>81758000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>80164000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>79551000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>78854000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78041000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76709000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75045000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>74720000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74745000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73023000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>71162000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70505000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>69372000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>68556000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>67051000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66026000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64382000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64212000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59521000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>58793000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +5883,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2346000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1962000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2156000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2185000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1892000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1904000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1983000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2108000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1790000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1795000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2359000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2348000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2080000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1973000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2002000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2039000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1797000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1602000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1980000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1691000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1657000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1454000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1752000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1663000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1578000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1366000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>844000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4438000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3898000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3519000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3127000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3171000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3240000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3328000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2990000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3894000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4123000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4365000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4279000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4629000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5186000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4160000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3166000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3431000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3818000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3236000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3429000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3427000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2780000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1504000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2176000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1029000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1479000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1692000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>799000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>182000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>779000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>549000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3281000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2739000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1964000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1991000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2846000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2630000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2611000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2573000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2331000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2796000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2672000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2292000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3359000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3286000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3022000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3203000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3176000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3105000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2782000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4466000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4870000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4145000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2738000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2618000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2742000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2861000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2395000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2998000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10536000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9419000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7965000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7769000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8439000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8507000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8274000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7907000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8598000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9027000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8827000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8366000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10347000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10820000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9262000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8342000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8609000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8962000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7815000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9497000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10277000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8616000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5899000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6248000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5523000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6003000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5665000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5375000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37111000</v>
+      </c>
+      <c r="E61" s="3">
         <v>35539000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>36007000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36433000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34590000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33359000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34175000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>33663000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31417000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30645000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30346000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30368000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27025000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25145000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25143000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24967000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24170000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23342000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22891000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20165000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>19632000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18958000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>19238000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19125000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>17864000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17066000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15883000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15683000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AK61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AL61" s="3">
         <v>11662000</v>
       </c>
       <c r="AM61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AN61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13340000</v>
+      </c>
+      <c r="E62" s="3">
         <v>15255000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13885000</v>
       </c>
-      <c r="F62" s="3">
-        <v>13470000</v>
-      </c>
       <c r="G62" s="3">
-        <v>13052000</v>
+        <v>13132000</v>
       </c>
       <c r="H62" s="3">
+        <v>13393000</v>
+      </c>
+      <c r="I62" s="3">
         <v>13540000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13361000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13460000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12837000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12443000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12269000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12642000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23147000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23451000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22965000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>23779000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24177000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>23977000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23143000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23620000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23514000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25333000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25468000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25109000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25499000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25790000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25060000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25016000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74767000</v>
+      </c>
+      <c r="E66" s="3">
         <v>71159000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69952000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69623000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>67839000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66642000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66950000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65984000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63814000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62593000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>61857000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61305000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62420000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>61317000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59271000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>58989000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58857000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58182000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55750000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55183000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55324000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>54808000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>52798000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>52675000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>48886000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48859000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>46608000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>46074000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,13 +7352,16 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1645000</v>
+        <v>497000</v>
       </c>
       <c r="E70" s="3">
         <v>1645000</v>
@@ -7212,13 +7379,13 @@
         <v>1645000</v>
       </c>
       <c r="J70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="K70" s="3">
         <v>1654000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>1978000</v>
       </c>
       <c r="M70" s="3">
         <v>1978000</v>
@@ -7230,7 +7397,7 @@
         <v>1978000</v>
       </c>
       <c r="P70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="Q70" s="3">
         <v>1977000</v>
@@ -7242,17 +7409,17 @@
         <v>1977000</v>
       </c>
       <c r="T70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="U70" s="3">
         <v>1235000</v>
       </c>
       <c r="V70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="W70" s="3">
         <v>1237000</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -7263,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>2193000</v>
@@ -7290,13 +7457,13 @@
         <v>2193000</v>
       </c>
       <c r="AJ70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AK70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AL70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AM70" s="3">
         <v>2191000</v>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AO70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10714000</v>
+      </c>
+      <c r="E72" s="3">
         <v>9165000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8709000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8662000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7567000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7486000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7326000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7166000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7499000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7399000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7553000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7456000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7454000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>7716000</v>
       </c>
       <c r="R72" s="3">
         <v>7716000</v>
       </c>
       <c r="S72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="T72" s="3">
         <v>7894000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7636000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8229000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8163000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8155000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7881000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8410000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8333000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8382000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8469000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8222000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8034000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17082000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15510000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15041000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14977000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13920000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14018000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13779000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13518000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13828000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13692000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13815000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13670000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13643000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13415000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13797000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13754000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13911000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13606000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14177000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14085000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14048000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13748000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14253000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13351000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13303000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13160000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10720000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10526000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1848000</v>
+      </c>
+      <c r="E81" s="3">
         <v>832000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>343000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1436000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>340000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>516000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>439000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>378000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>155000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>354000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>310000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>415000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>241000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>110000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>523000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-341000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>318000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>259000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>526000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-288000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>318000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>183000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>143000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>471000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>392000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>278000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>513000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>276000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>218000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>470000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>278000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>362000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>346000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E83" s="3">
         <v>729000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>747000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>707000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>329000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>663000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>695000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>676000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>312000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>761000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>592000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>624000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>656000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>761000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>592000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>624000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>579000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>619000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>548000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>542000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>517000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>507000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>504000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>501000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>487000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>479000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>339000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>498000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>301000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>565000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>595000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>479000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>524000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>543000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>528000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>520000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>523000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2122000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>882000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1224000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1170000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2472000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>329000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1043000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>855000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1834000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>802000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-90000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1104000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>874000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>446000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>792000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>427000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>958000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>72000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>192000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>446000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>310000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>315000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>510000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>388000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>210000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>906000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>401000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>816000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>899000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>554000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>884000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>754000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1891000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1504000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1712000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1408000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1496000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1511000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1842000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1491000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1628000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1374000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1439000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1427000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-986000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,58 +9987,59 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>318000</v>
+        <v>319000</v>
       </c>
       <c r="E96" s="3">
         <v>318000</v>
       </c>
       <c r="F96" s="3">
+        <v>318000</v>
+      </c>
+      <c r="G96" s="3">
         <v>319000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>302000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>301000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>300000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>295000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>279000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>278000</v>
       </c>
       <c r="M96" s="3">
         <v>278000</v>
       </c>
       <c r="N96" s="3">
+        <v>278000</v>
+      </c>
+      <c r="O96" s="3">
         <v>277000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-263000</v>
       </c>
       <c r="P96" s="3">
         <v>-263000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="R96" s="3">
         <v>-262000</v>
       </c>
       <c r="S96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="T96" s="3">
         <v>-247000</v>
@@ -9818,31 +10051,31 @@
         <v>-247000</v>
       </c>
       <c r="W96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="X96" s="3">
         <v>-237000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-228000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-226000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-216000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AF96" s="3">
         <v>-197000</v>
@@ -9854,25 +10087,28 @@
         <v>-197000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AL96" s="3">
         <v>-177000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,124 +10461,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-513000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-383000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1374000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>310000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1201000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>577000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>988000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>567000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-339000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-97000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1316000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1049000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>713000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>914000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>205000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>939000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>724000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2271000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1511000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1080000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>424000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2231000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>345000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2907000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>642000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1009000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>393000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>491000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>111000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>112000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>195000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="E102" s="3">
         <v>118000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1129000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1224000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>41000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-156000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-488000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>755000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>83000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>251000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-640000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-79000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>684000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>110000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-111000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-160000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-131000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>440000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-305000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>301000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-432000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-812000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1268000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-478000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>283000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-120000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>233000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>73000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>997000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>19000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>55000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>12000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-27000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>EIX</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4103000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5213000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5750000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4543000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3811000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3984000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5201000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4336000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4078000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3706000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4702000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3964000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3966000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4016000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5228000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4008000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3968000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3331000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5299000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3315000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2960000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3157000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4644000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2987000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2790000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2970000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3741000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2812000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2824000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4269000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2815000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2564000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3220000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2965000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2463000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2884000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3767000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1987000</v>
+      </c>
+      <c r="E9" s="3">
         <v>503000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2876000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2737000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2030000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>358000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3247000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2519000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2325000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-872000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2870000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2388000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2402000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2446000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3464000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2665000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2524000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1984000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3310000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2037000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1857000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1843000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3065000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1830000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1809000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1691000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2549000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1730000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1887000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1791000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2980000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1831000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1601000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1944000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2504000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1881000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1388000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1729000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2459000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2116000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4710000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2874000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1806000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1781000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3626000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1954000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1817000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1753000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4578000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1832000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1576000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1564000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1570000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1764000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1343000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1444000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1347000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1989000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1278000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1103000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1314000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1579000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1157000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>981000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1279000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1192000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1082000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>937000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1218000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1289000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>984000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>963000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1276000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1168000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1084000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1075000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1155000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1308000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,16 +1234,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>463000</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1238,11 +1252,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>416000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1250,11 +1264,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>358000</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,246 +1476,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-904000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>421000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>41000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1255000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>82000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>81000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>37000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>651000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>144000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>536000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>53000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>151000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>45000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>942000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>118000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>478000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>58000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1405000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>43000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>53000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>39000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1354000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>65000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>84000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>425000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>170000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2687000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>716000</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>16000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>5000</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>834000</v>
+      </c>
+      <c r="E15" s="3">
         <v>807000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>862000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>826000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>742000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>728000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>710000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>726000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>702000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>664000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>665000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>650000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>656000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>639000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>738000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>601000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>583000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>561000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>599000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>533000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>525000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>504000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>490000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>489000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>484000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>470000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>459000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>321000</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>480000</v>
       </c>
       <c r="AF15" s="3">
         <v>480000</v>
       </c>
       <c r="AG15" s="3">
+        <v>480000</v>
+      </c>
+      <c r="AH15" s="3">
         <v>466000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>463000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>462000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>506000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>524000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>512000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>499000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>503000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2975000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3339000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3878000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3711000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2917000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3087000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4103000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3377000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3160000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2749000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3648000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3161000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3172000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3252000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5272000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3504000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3709000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2710000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5427000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2730000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2561000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2363000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5023000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2487000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2488000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2683000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3105000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2312000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2472000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5050000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3530000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2395000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2234000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3258000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3119000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2495000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2317000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3072000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1128000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1874000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1872000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>832000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>894000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>897000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1098000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>959000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>918000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>957000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1054000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>803000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>794000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>764000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-44000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>504000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>259000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>621000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-128000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>585000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>399000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>794000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-379000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>500000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>302000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>287000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>636000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>500000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>352000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2041000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>739000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>420000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>330000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-38000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>553000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>470000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>471000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>567000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>695000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,603 +2051,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-23000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-46000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-58000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-40000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-53000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-49000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-35000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>129000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>85000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>66000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>68000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>42000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>47000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>76000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>72000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>34000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>84000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>81000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>52000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>42000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>58000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>55000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>38000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>21000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>76000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>49000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>34000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>41000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>24000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>33000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>11000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2017000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2704000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2780000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1716000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1683000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1635000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1848000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1738000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1669000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1654000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1753000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1488000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1484000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1549000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>802000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1162000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>951000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1242000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>538000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1209000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1013000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1345000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>212000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1085000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>855000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>816000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>894000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>888000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1719000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1380000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1064000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>860000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>520000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1137000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1024000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1101000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1268000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E22" s="3">
         <v>246000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>488000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>504000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>301000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>468000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>477000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>480000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>444000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>426000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>433000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>392000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>361000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>350000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>302000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>271000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>246000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>231000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>245000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>232000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>217000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>226000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>222000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>229000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>225000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>222000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>214000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>211000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>194000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>196000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>188000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>180000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>170000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>166000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>162000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>159000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>152000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>150000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>147000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>632000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2530000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1007000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>329000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1884000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>343000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>584000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>498000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-124000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>445000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>132000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>405000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>323000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>543000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-261000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>299000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>81000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>432000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-326000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>429000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>254000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>602000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-517000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>352000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>129000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>107000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>480000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>344000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>196000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2216000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>627000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>289000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>211000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-170000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>432000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>335000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>352000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>428000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>571000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E24" s="3">
         <v>682000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>175000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>448000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>68000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>59000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-113000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>67000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-23000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>73000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-187000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-55000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-139000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-29000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>68000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-36000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>50000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-275000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-22000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-78000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-112000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-782000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>83000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-31000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-102000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-69000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>26000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>64000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1848000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>832000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>343000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1436000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>340000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>516000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>439000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>378000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>155000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>354000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>310000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>470000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-74000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>292000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>136000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>571000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-297000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>361000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>290000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>552000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-242000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>348000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>213000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>173000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>502000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>422000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>308000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1434000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>544000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>298000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>242000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>501000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>309000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>392000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>364000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>451000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1846000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>832000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>343000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1435000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>340000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>516000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>439000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>378000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>155000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>354000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>310000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>415000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-101000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>241000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>110000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>523000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-341000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>318000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>259000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>526000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-288000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>318000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>183000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>143000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>471000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>392000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>278000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1464000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>513000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>276000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-79000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>470000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>278000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>362000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>333000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3160,17 +3221,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3178,11 +3239,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>34000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3190,12 +3251,12 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-466000</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
         <v>0</v>
       </c>
@@ -3203,13 +3264,16 @@
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>13000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E32" s="3">
         <v>23000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>46000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>58000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>40000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>53000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>49000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>35000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-85000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-66000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-68000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-42000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-47000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-76000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-72000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-84000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-81000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-52000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-58000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-76000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-49000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-51000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-24000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1848000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>832000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>343000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1436000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>340000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>516000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>439000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>378000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>155000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>354000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>310000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>415000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-101000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>241000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>110000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>523000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-341000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>318000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>259000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>526000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-288000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>318000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>183000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>143000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>471000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>392000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>278000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>513000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>276000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-545000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>470000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>278000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>362000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>346000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1848000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>832000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>343000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1436000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>340000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>516000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>439000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>378000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>155000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>354000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>310000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>415000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-101000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>241000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>110000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>523000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-341000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>318000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>259000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>526000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-288000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>318000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>183000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>143000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>471000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>392000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>278000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>513000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>276000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-545000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>470000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>278000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>362000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>346000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E41" s="3">
         <v>158000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>364000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>140000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1318000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>465000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>992000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>446000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>195000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>836000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>914000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>232000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>122000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>231000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>390000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>524000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>84000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>389000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>87000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>92000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>524000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1337000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>547000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>257000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>328000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>144000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>71000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>99000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>105000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1091000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>117000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>98000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>150000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>96000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>84000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,722 +4460,743 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2599000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2701000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3443000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2829000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2669000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3017000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3982000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3027000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2667000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2758000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3292000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2473000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2217000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1695000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2259000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1547000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1312000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1398000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1612000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1314000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1696000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1906000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2314000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1044000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>926000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>906000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1226000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>922000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>908000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>921000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>954000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>760000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>941000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1105000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>833000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>688000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>714000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>999000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>542000</v>
+      </c>
+      <c r="E44" s="3">
         <v>535000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>524000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>523000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>539000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>538000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>533000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>534000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>519000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>527000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>505000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>511000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>500000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>474000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>439000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>438000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>434000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>420000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>412000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>406000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>416000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>405000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>387000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>382000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>363000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>364000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>348000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>331000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>312000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>282000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>261000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>252000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>247000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>242000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>229000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>235000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>237000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>239000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3027000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3621000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3189000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3332000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2579000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3264000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2558000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4344000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3389000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3034000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2887000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4146000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3344000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3987000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3511000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3546000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3296000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3283000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3480000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3117000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2827000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2663000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3062000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2846000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2285000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2222000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2541000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2426000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2451000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2012000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1840000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1952000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1880000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1455000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1307000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1380000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>971000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1074000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1212000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7176000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7686000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7728000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6950000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7427000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7155000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7444000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8512000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7878000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6811000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7235000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7416000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7210000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7070000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6441000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5653000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5273000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5491000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6028000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4921000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5328000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5061000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5855000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4796000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4911000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3560000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4662000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3936000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3999000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3359000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3383000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3257000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2992000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3729000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2758000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2546000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2046000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2123000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2605000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E47" s="3">
         <v>51000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>70000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>57000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>71000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>62000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>54000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>81000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>72000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4470000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4378000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4332000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4818000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5118000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4999000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5040000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4897000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4961000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4735000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4650000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4341000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4626000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4568000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4504000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4367000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>4183000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>4389000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4378000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4415000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4513000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>4487000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4468000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4441000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4325000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>4452000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65362000</v>
+      </c>
+      <c r="E48" s="3">
         <v>64359000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62968000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62155000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>61323000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>60310000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59478000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>58550000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57894000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57183000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>56346000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55557000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>55516000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>54928000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54129000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>53446000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>52849000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>52632000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>51286000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>50036000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>49355000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>48927000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>47582000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>46225000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>45503000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>44978000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>43940000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>43156000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>42697000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>41348000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>40412000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>39831000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>39235000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>39050000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>37961000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>37512000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>37168000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>37000000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>36231000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8863000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8970000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9037000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9158000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9063000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9171000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9117000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9027000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8959000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8813000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7728000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7885000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7913000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11573000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11761000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11614000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11780000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11504000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10710000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11165000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10925000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10423000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10384000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11380000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11271000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11218000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11042000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7925000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7730000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7825000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5379000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5354000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5301000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5288000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>8386000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>8227000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>8085000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>7871000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>8269000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94475000</v>
+      </c>
+      <c r="E54" s="3">
         <v>94026000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90489000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>88813000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88420000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>85579000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>84749000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>84818000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>83599000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>81758000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>80164000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>79551000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78854000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78041000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>76709000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>75045000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74720000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>74745000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>73023000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>71162000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70505000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>69372000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>68556000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>67051000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>66026000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64382000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64212000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59521000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>58793000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>56715000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>53563000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>52820000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>51943000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>52580000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>53592000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>52753000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51740000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>51319000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>51557000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2413000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2344000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2346000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1962000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2156000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2185000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1892000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1904000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1983000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2108000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1790000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1795000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2359000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2348000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2080000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1973000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2002000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2039000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1797000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1602000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1980000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1691000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1657000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1454000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1752000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1663000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1578000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1366000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1511000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1288000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1255000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1033000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1503000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1104000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1113000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>844000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1342000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1180000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4358000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4438000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3898000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3519000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3127000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3171000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3240000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3328000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2990000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3894000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4123000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4365000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4279000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4629000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5186000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4160000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3166000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3431000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3818000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3236000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3429000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3427000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2780000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1504000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2176000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1029000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1479000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1692000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>799000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>182000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>779000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>549000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2874000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1491000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1147000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1276000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>2288000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2425000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3281000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2739000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1964000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1991000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2846000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2630000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2611000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2573000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2331000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2796000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2672000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2292000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3359000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3286000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3022000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3203000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3176000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3105000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2782000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4466000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4870000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4145000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2738000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2618000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2742000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2861000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2395000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2998000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3085000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3249000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2888000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3065000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2691000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2814000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2342000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2296000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2282000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2524000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9700000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10536000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9419000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7965000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7769000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8439000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8507000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8274000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7907000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8598000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9027000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8827000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8366000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10347000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10820000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9262000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8342000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8609000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8962000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7815000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9497000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10277000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8616000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5899000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6248000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5523000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6003000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5665000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5375000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5395000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4719000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4922000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4647000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7068000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5409000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4602000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4416000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5912000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5342000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38339000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37111000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>35539000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36007000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36433000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34590000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33359000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34175000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33663000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31417000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>30645000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30346000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30368000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27025000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>25145000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>25143000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>24967000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24170000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23342000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22891000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20165000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>19632000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18958000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>19238000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19125000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17864000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>17066000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15883000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15683000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14632000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14629000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13845000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13367000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>11642000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11638000</v>
-      </c>
-      <c r="AL61" s="3">
-        <v>11662000</v>
       </c>
       <c r="AM61" s="3">
         <v>11662000</v>
       </c>
       <c r="AN61" s="3">
+        <v>11662000</v>
+      </c>
+      <c r="AO61" s="3">
         <v>10175000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10407000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13613000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13340000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15255000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13885000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13132000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13393000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13540000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13361000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13460000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12837000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12443000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12269000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12642000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23147000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23451000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>22965000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>23779000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>24177000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23977000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23143000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23620000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>23514000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>25333000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>25468000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25109000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25499000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25790000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>25060000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>25016000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>24036000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19926000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>20081000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>20040000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>19985000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>21922000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>21677000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>21413000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>21040000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>21803000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75591000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74767000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71159000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69952000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69623000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>67839000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66642000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>66950000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65984000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63814000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62593000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>61857000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>61305000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62420000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>61317000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59271000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>58989000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58857000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>58182000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55750000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>55183000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>55324000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>54808000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>52798000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52675000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>48886000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>48859000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>46608000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46074000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44063000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>39274000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38848000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>38054000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>38716000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>38982000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37953000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>37498000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>37132000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>37552000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,16 +7520,19 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E70" s="3">
         <v>497000</v>
-      </c>
-      <c r="E70" s="3">
-        <v>1645000</v>
       </c>
       <c r="F70" s="3">
         <v>1645000</v>
@@ -7382,13 +7550,13 @@
         <v>1645000</v>
       </c>
       <c r="K70" s="3">
+        <v>1645000</v>
+      </c>
+      <c r="L70" s="3">
         <v>1654000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1673000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>1978000</v>
       </c>
       <c r="N70" s="3">
         <v>1978000</v>
@@ -7400,7 +7568,7 @@
         <v>1978000</v>
       </c>
       <c r="Q70" s="3">
-        <v>1977000</v>
+        <v>1978000</v>
       </c>
       <c r="R70" s="3">
         <v>1977000</v>
@@ -7412,17 +7580,17 @@
         <v>1977000</v>
       </c>
       <c r="U70" s="3">
-        <v>1235000</v>
+        <v>1977000</v>
       </c>
       <c r="V70" s="3">
         <v>1235000</v>
       </c>
       <c r="W70" s="3">
+        <v>1235000</v>
+      </c>
+      <c r="X70" s="3">
         <v>1237000</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -7433,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>2193000</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>2193000</v>
@@ -7460,13 +7628,13 @@
         <v>2193000</v>
       </c>
       <c r="AK70" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="AL70" s="3">
         <v>2194000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>2654000</v>
-      </c>
-      <c r="AM70" s="3">
-        <v>2191000</v>
       </c>
       <c r="AN70" s="3">
         <v>2191000</v>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>2191000</v>
       </c>
+      <c r="AP70" s="3">
+        <v>2191000</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10899000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10714000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9165000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8709000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8662000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7567000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7486000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7326000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7166000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7499000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7399000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7553000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7456000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7454000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7295000</v>
-      </c>
-      <c r="R72" s="3">
-        <v>7716000</v>
       </c>
       <c r="S72" s="3">
         <v>7716000</v>
       </c>
       <c r="T72" s="3">
+        <v>7716000</v>
+      </c>
+      <c r="U72" s="3">
         <v>7894000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7636000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8229000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8163000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8155000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7881000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8410000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8333000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8382000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>8469000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>8222000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8034000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7964000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9597000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9286000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9211000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>9188000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>9944000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9679000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9590000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9544000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9362000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17237000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17082000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15510000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15041000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14977000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13920000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14018000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13779000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13518000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13828000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13692000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13815000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13670000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13643000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13415000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13797000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13754000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13911000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13606000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14177000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14085000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14048000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13748000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14253000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13351000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13303000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13160000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10720000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10526000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10459000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12096000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11779000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11696000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11671000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12416000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12146000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12051000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11996000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11814000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1848000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>832000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>343000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1436000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>340000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>516000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>439000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>378000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>155000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>354000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>310000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>415000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-101000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>241000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>110000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>523000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-341000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>318000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>259000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>526000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-288000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>318000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>183000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>143000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>471000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>392000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>278000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1430000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>513000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>276000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>218000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-545000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>470000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>278000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>362000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>346000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>421000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>742000</v>
+      </c>
+      <c r="E83" s="3">
         <v>267000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>729000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>747000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>707000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>329000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>663000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>695000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>676000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>312000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>761000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>592000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>624000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>656000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>761000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>592000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>624000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>579000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>619000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>548000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>542000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>517000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>507000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>504000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>501000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>487000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>479000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>339000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>498000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>301000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>565000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>595000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>479000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>524000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>543000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>528000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>520000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>523000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>550000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1427000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1572000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2122000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>882000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1224000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1170000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2472000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>329000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1043000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>855000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1834000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>802000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-90000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1104000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>874000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>446000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>792000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>427000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>958000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1446000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>72000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>192000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>446000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>310000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>315000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>510000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1415000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>388000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>210000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>906000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1054000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>401000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>816000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>899000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1260000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>554000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>884000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>754000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1070000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1539000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1891000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1504000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1712000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1408000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1496000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1511000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1421000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1279000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1280000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1387000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1324000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1572000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1498000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1501000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1207000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1557000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1355000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1235000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1358000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1587000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1383000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1246000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1380000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1262000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1161000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1268000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1082000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1022000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1168000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-911000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-810000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1883000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>1812000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1890000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1588000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1842000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1491000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1628000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1374000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1439000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1427000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1394000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1276000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1339000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1244000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1345000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1477000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1157000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1130000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1282000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1277000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1302000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1114000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1278000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1209000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-986000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1226000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1025000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1097000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-839000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-717000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-937000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-796000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,61 +10221,62 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E96" s="3">
         <v>319000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>318000</v>
       </c>
       <c r="F96" s="3">
         <v>318000</v>
       </c>
       <c r="G96" s="3">
+        <v>318000</v>
+      </c>
+      <c r="H96" s="3">
         <v>319000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>302000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>301000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>300000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>295000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>279000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>278000</v>
       </c>
       <c r="N96" s="3">
         <v>278000</v>
       </c>
       <c r="O96" s="3">
+        <v>278000</v>
+      </c>
+      <c r="P96" s="3">
         <v>277000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-263000</v>
       </c>
       <c r="Q96" s="3">
         <v>-263000</v>
       </c>
       <c r="R96" s="3">
-        <v>-262000</v>
+        <v>-263000</v>
       </c>
       <c r="S96" s="3">
         <v>-262000</v>
       </c>
       <c r="T96" s="3">
-        <v>-247000</v>
+        <v>-262000</v>
       </c>
       <c r="U96" s="3">
         <v>-247000</v>
@@ -10054,31 +10288,31 @@
         <v>-247000</v>
       </c>
       <c r="X96" s="3">
-        <v>-237000</v>
+        <v>-247000</v>
       </c>
       <c r="Y96" s="3">
         <v>-237000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-228000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-226000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-216000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-195000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-199000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-200000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-197000</v>
       </c>
       <c r="AG96" s="3">
         <v>-197000</v>
@@ -10090,25 +10324,28 @@
         <v>-197000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-197000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-177000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-176000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-177000</v>
       </c>
       <c r="AM96" s="3">
         <v>-177000</v>
       </c>
       <c r="AN96" s="3">
+        <v>-177000</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-156000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,127 +10707,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E100" s="3">
         <v>93000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-513000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-383000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1374000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>310000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1201000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>577000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>988000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>567000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-339000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-97000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1316000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>713000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>914000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>205000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>939000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>724000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2271000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1511000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1080000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>424000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2231000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>345000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2907000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>642000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1009000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>393000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-57000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>491000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-745000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1183000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-399000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>111000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>112000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>195000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-302000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-177000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>118000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1129000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1224000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>41000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-156000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-488000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>755000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>83000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>251000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-640000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-79000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>684000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>110000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-111000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-160000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-131000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>440000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-305000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>301000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-432000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-812000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1268000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-478000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>283000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-120000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>233000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>73000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-28000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1026000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>997000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>19000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-53000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>55000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>12000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-27000</v>
       </c>
     </row>
